--- a/academias/Biología - Estadisticos 20222.xlsx
+++ b/academias/Biología - Estadisticos 20222.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="31">
   <si>
     <t>Docente</t>
   </si>
@@ -87,33 +87,21 @@
     <t>4ASV</t>
   </si>
   <si>
-    <t>6AEM</t>
-  </si>
-  <si>
     <t>6ALCM</t>
   </si>
   <si>
-    <t>6APM</t>
-  </si>
-  <si>
-    <t>6ARHM</t>
-  </si>
-  <si>
-    <t>6BEM</t>
-  </si>
-  <si>
     <t>6BLCM</t>
   </si>
   <si>
+    <t>4ALCV</t>
+  </si>
+  <si>
+    <t>4ARHV</t>
+  </si>
+  <si>
     <t>6ALCV</t>
   </si>
   <si>
-    <t>4ALCV</t>
-  </si>
-  <si>
-    <t>4ARHV</t>
-  </si>
-  <si>
     <t>4APV</t>
   </si>
   <si>
@@ -121,9 +109,6 @@
   </si>
   <si>
     <t>TEMAS DE BIOLOGÍA CONTEMPORÁNEA</t>
-  </si>
-  <si>
-    <t>TEMAS DE CIENCIAS DE LA SALUD</t>
   </si>
 </sst>
 </file>
@@ -487,7 +472,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K26"/>
+  <dimension ref="A1:K15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -540,7 +525,7 @@
         <v>15</v>
       </c>
       <c r="C2" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="D2">
         <v>31</v>
@@ -575,7 +560,7 @@
         <v>16</v>
       </c>
       <c r="C3" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="D3">
         <v>41</v>
@@ -610,7 +595,7 @@
         <v>17</v>
       </c>
       <c r="C4" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="D4">
         <v>27</v>
@@ -645,7 +630,7 @@
         <v>18</v>
       </c>
       <c r="C5" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="D5">
         <v>38</v>
@@ -680,7 +665,7 @@
         <v>19</v>
       </c>
       <c r="C6" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="D6">
         <v>28</v>
@@ -715,7 +700,7 @@
         <v>20</v>
       </c>
       <c r="C7" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="D7">
         <v>41</v>
@@ -750,7 +735,7 @@
         <v>21</v>
       </c>
       <c r="C8" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="D8">
         <v>32</v>
@@ -785,7 +770,7 @@
         <v>22</v>
       </c>
       <c r="C9" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="D9">
         <v>14</v>
@@ -820,18 +805,30 @@
         <v>23</v>
       </c>
       <c r="C10" t="s">
+        <v>30</v>
+      </c>
+      <c r="D10">
         <v>34</v>
       </c>
-      <c r="D10">
-        <v>0</v>
-      </c>
       <c r="E10">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="F10">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="G10" s="1">
+        <v>97.06</v>
+      </c>
+      <c r="H10" s="1">
+        <v>2.94</v>
+      </c>
+      <c r="I10" s="2">
+        <v>9</v>
       </c>
       <c r="J10">
+        <v>0</v>
+      </c>
+      <c r="K10" s="1">
         <v>0</v>
       </c>
     </row>
@@ -840,426 +837,170 @@
         <v>11</v>
       </c>
       <c r="B11" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C11" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="D11">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="E11">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="F11">
         <v>0</v>
       </c>
+      <c r="G11" s="1">
+        <v>100</v>
+      </c>
+      <c r="H11" s="1">
+        <v>0</v>
+      </c>
+      <c r="I11" s="2">
+        <v>9.800000000000001</v>
+      </c>
       <c r="J11">
+        <v>0</v>
+      </c>
+      <c r="K11" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:11">
       <c r="A12" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B12" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C12" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="D12">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E12">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="F12">
+        <v>7</v>
+      </c>
+      <c r="G12" s="1">
+        <v>78.79000000000001</v>
+      </c>
+      <c r="H12" s="1">
+        <v>21.21</v>
+      </c>
+      <c r="I12" s="2">
+        <v>7.2</v>
+      </c>
+      <c r="J12">
         <v>1</v>
       </c>
-      <c r="G12" s="1">
-        <v>97.06</v>
-      </c>
-      <c r="H12" s="1">
-        <v>2.94</v>
-      </c>
-      <c r="I12" s="2">
-        <v>9</v>
-      </c>
-      <c r="J12">
-        <v>0</v>
-      </c>
       <c r="K12" s="1">
-        <v>0</v>
+        <v>3.03</v>
       </c>
     </row>
     <row r="13" spans="1:11">
       <c r="A13" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B13" t="s">
+        <v>26</v>
+      </c>
+      <c r="C13" t="s">
+        <v>29</v>
+      </c>
+      <c r="D13">
+        <v>29</v>
+      </c>
+      <c r="E13">
         <v>24</v>
       </c>
-      <c r="C13" t="s">
-        <v>35</v>
-      </c>
-      <c r="D13">
-        <v>0</v>
-      </c>
-      <c r="E13">
-        <v>0</v>
-      </c>
       <c r="F13">
-        <v>0</v>
+        <v>5</v>
+      </c>
+      <c r="G13" s="1">
+        <v>82.76000000000001</v>
+      </c>
+      <c r="H13" s="1">
+        <v>17.24</v>
+      </c>
+      <c r="I13" s="2">
+        <v>7.1</v>
       </c>
       <c r="J13">
+        <v>0</v>
+      </c>
+      <c r="K13" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:11">
       <c r="A14" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B14" t="s">
+        <v>27</v>
+      </c>
+      <c r="C14" t="s">
+        <v>30</v>
+      </c>
+      <c r="D14">
+        <v>26</v>
+      </c>
+      <c r="E14">
         <v>25</v>
       </c>
-      <c r="C14" t="s">
-        <v>34</v>
-      </c>
-      <c r="D14">
-        <v>0</v>
-      </c>
-      <c r="E14">
-        <v>0</v>
-      </c>
       <c r="F14">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="G14" s="1">
+        <v>96.15000000000001</v>
+      </c>
+      <c r="H14" s="1">
+        <v>3.85</v>
+      </c>
+      <c r="I14" s="2">
+        <v>9.1</v>
       </c>
       <c r="J14">
+        <v>0</v>
+      </c>
+      <c r="K14" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:11">
       <c r="A15" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B15" t="s">
+        <v>28</v>
+      </c>
+      <c r="C15" t="s">
+        <v>29</v>
+      </c>
+      <c r="D15">
         <v>25</v>
       </c>
-      <c r="C15" t="s">
-        <v>35</v>
-      </c>
-      <c r="D15">
-        <v>0</v>
-      </c>
       <c r="E15">
         <v>0</v>
       </c>
       <c r="F15">
-        <v>0</v>
+        <v>25</v>
+      </c>
+      <c r="G15" s="1">
+        <v>0</v>
+      </c>
+      <c r="H15" s="1">
+        <v>100</v>
       </c>
       <c r="J15">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11">
-      <c r="A16" t="s">
-        <v>11</v>
-      </c>
-      <c r="B16" t="s">
-        <v>26</v>
-      </c>
-      <c r="C16" t="s">
-        <v>34</v>
-      </c>
-      <c r="D16">
-        <v>0</v>
-      </c>
-      <c r="E16">
-        <v>0</v>
-      </c>
-      <c r="F16">
-        <v>0</v>
-      </c>
-      <c r="J16">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11">
-      <c r="A17" t="s">
-        <v>11</v>
-      </c>
-      <c r="B17" t="s">
-        <v>26</v>
-      </c>
-      <c r="C17" t="s">
-        <v>35</v>
-      </c>
-      <c r="D17">
-        <v>0</v>
-      </c>
-      <c r="E17">
-        <v>0</v>
-      </c>
-      <c r="F17">
-        <v>0</v>
-      </c>
-      <c r="J17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11">
-      <c r="A18" t="s">
-        <v>11</v>
-      </c>
-      <c r="B18" t="s">
-        <v>27</v>
-      </c>
-      <c r="C18" t="s">
-        <v>34</v>
-      </c>
-      <c r="D18">
-        <v>0</v>
-      </c>
-      <c r="E18">
-        <v>0</v>
-      </c>
-      <c r="F18">
-        <v>0</v>
-      </c>
-      <c r="J18">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:11">
-      <c r="A19" t="s">
-        <v>11</v>
-      </c>
-      <c r="B19" t="s">
-        <v>27</v>
-      </c>
-      <c r="C19" t="s">
-        <v>35</v>
-      </c>
-      <c r="D19">
-        <v>0</v>
-      </c>
-      <c r="E19">
-        <v>0</v>
-      </c>
-      <c r="F19">
-        <v>0</v>
-      </c>
-      <c r="J19">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:11">
-      <c r="A20" t="s">
-        <v>11</v>
-      </c>
-      <c r="B20" t="s">
-        <v>28</v>
-      </c>
-      <c r="C20" t="s">
-        <v>34</v>
-      </c>
-      <c r="D20">
-        <v>32</v>
-      </c>
-      <c r="E20">
-        <v>32</v>
-      </c>
-      <c r="F20">
-        <v>0</v>
-      </c>
-      <c r="G20" s="1">
-        <v>100</v>
-      </c>
-      <c r="H20" s="1">
-        <v>0</v>
-      </c>
-      <c r="I20" s="2">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="J20">
-        <v>0</v>
-      </c>
-      <c r="K20" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:11">
-      <c r="A21" t="s">
-        <v>11</v>
-      </c>
-      <c r="B21" t="s">
-        <v>28</v>
-      </c>
-      <c r="C21" t="s">
-        <v>35</v>
-      </c>
-      <c r="D21">
-        <v>0</v>
-      </c>
-      <c r="E21">
-        <v>0</v>
-      </c>
-      <c r="F21">
-        <v>0</v>
-      </c>
-      <c r="J21">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:11">
-      <c r="A22" t="s">
-        <v>11</v>
-      </c>
-      <c r="B22" t="s">
-        <v>29</v>
-      </c>
-      <c r="C22" t="s">
-        <v>35</v>
-      </c>
-      <c r="D22">
-        <v>0</v>
-      </c>
-      <c r="E22">
-        <v>0</v>
-      </c>
-      <c r="F22">
-        <v>0</v>
-      </c>
-      <c r="J22">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:11">
-      <c r="A23" t="s">
-        <v>12</v>
-      </c>
-      <c r="B23" t="s">
-        <v>30</v>
-      </c>
-      <c r="C23" t="s">
-        <v>33</v>
-      </c>
-      <c r="D23">
-        <v>33</v>
-      </c>
-      <c r="E23">
-        <v>0</v>
-      </c>
-      <c r="F23">
-        <v>33</v>
-      </c>
-      <c r="G23" s="1">
-        <v>0</v>
-      </c>
-      <c r="H23" s="1">
-        <v>100</v>
-      </c>
-      <c r="J23">
-        <v>33</v>
-      </c>
-      <c r="K23" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="24" spans="1:11">
-      <c r="A24" t="s">
-        <v>12</v>
-      </c>
-      <c r="B24" t="s">
-        <v>31</v>
-      </c>
-      <c r="C24" t="s">
-        <v>33</v>
-      </c>
-      <c r="D24">
-        <v>29</v>
-      </c>
-      <c r="E24">
-        <v>0</v>
-      </c>
-      <c r="F24">
-        <v>29</v>
-      </c>
-      <c r="G24" s="1">
-        <v>0</v>
-      </c>
-      <c r="H24" s="1">
-        <v>100</v>
-      </c>
-      <c r="J24">
-        <v>29</v>
-      </c>
-      <c r="K24" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="25" spans="1:11">
-      <c r="A25" t="s">
-        <v>13</v>
-      </c>
-      <c r="B25" t="s">
-        <v>29</v>
-      </c>
-      <c r="C25" t="s">
-        <v>34</v>
-      </c>
-      <c r="D25">
-        <v>26</v>
-      </c>
-      <c r="E25">
-        <v>0</v>
-      </c>
-      <c r="F25">
-        <v>26</v>
-      </c>
-      <c r="G25" s="1">
-        <v>0</v>
-      </c>
-      <c r="H25" s="1">
-        <v>100</v>
-      </c>
-      <c r="J25">
-        <v>26</v>
-      </c>
-      <c r="K25" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="26" spans="1:11">
-      <c r="A26" t="s">
-        <v>14</v>
-      </c>
-      <c r="B26" t="s">
-        <v>32</v>
-      </c>
-      <c r="C26" t="s">
-        <v>33</v>
-      </c>
-      <c r="D26">
         <v>25</v>
       </c>
-      <c r="E26">
-        <v>0</v>
-      </c>
-      <c r="F26">
-        <v>25</v>
-      </c>
-      <c r="G26" s="1">
-        <v>0</v>
-      </c>
-      <c r="H26" s="1">
-        <v>100</v>
-      </c>
-      <c r="J26">
-        <v>25</v>
-      </c>
-      <c r="K26" s="1">
+      <c r="K15" s="1">
         <v>100</v>
       </c>
     </row>
@@ -1270,7 +1011,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K26"/>
+  <dimension ref="A1:K15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -1323,7 +1064,7 @@
         <v>15</v>
       </c>
       <c r="C2" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="D2">
         <v>31</v>
@@ -1355,7 +1096,7 @@
         <v>16</v>
       </c>
       <c r="C3" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="D3">
         <v>41</v>
@@ -1387,7 +1128,7 @@
         <v>17</v>
       </c>
       <c r="C4" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="D4">
         <v>27</v>
@@ -1419,7 +1160,7 @@
         <v>18</v>
       </c>
       <c r="C5" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="D5">
         <v>38</v>
@@ -1451,7 +1192,7 @@
         <v>19</v>
       </c>
       <c r="C6" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="D6">
         <v>28</v>
@@ -1483,7 +1224,7 @@
         <v>20</v>
       </c>
       <c r="C7" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="D7">
         <v>41</v>
@@ -1515,7 +1256,7 @@
         <v>21</v>
       </c>
       <c r="C8" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="D8">
         <v>32</v>
@@ -1547,7 +1288,7 @@
         <v>22</v>
       </c>
       <c r="C9" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="D9">
         <v>14</v>
@@ -1579,19 +1320,28 @@
         <v>23</v>
       </c>
       <c r="C10" t="s">
+        <v>30</v>
+      </c>
+      <c r="D10">
         <v>34</v>
       </c>
-      <c r="D10">
-        <v>0</v>
-      </c>
       <c r="E10">
         <v>0</v>
       </c>
       <c r="F10">
-        <v>0</v>
+        <v>34</v>
+      </c>
+      <c r="G10" s="1">
+        <v>0</v>
+      </c>
+      <c r="H10" s="1">
+        <v>100</v>
       </c>
       <c r="J10">
-        <v>0</v>
+        <v>34</v>
+      </c>
+      <c r="K10" s="1">
+        <v>100</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -1599,42 +1349,51 @@
         <v>11</v>
       </c>
       <c r="B11" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C11" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="D11">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="E11">
         <v>0</v>
       </c>
       <c r="F11">
-        <v>0</v>
+        <v>32</v>
+      </c>
+      <c r="G11" s="1">
+        <v>0</v>
+      </c>
+      <c r="H11" s="1">
+        <v>100</v>
       </c>
       <c r="J11">
-        <v>0</v>
+        <v>32</v>
+      </c>
+      <c r="K11" s="1">
+        <v>100</v>
       </c>
     </row>
     <row r="12" spans="1:11">
       <c r="A12" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B12" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C12" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="D12">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E12">
         <v>0</v>
       </c>
       <c r="F12">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G12" s="1">
         <v>0</v>
@@ -1643,7 +1402,7 @@
         <v>100</v>
       </c>
       <c r="J12">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="K12" s="1">
         <v>100</v>
@@ -1651,368 +1410,97 @@
     </row>
     <row r="13" spans="1:11">
       <c r="A13" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C13" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="D13">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="E13">
         <v>0</v>
       </c>
       <c r="F13">
-        <v>0</v>
+        <v>29</v>
+      </c>
+      <c r="G13" s="1">
+        <v>0</v>
+      </c>
+      <c r="H13" s="1">
+        <v>100</v>
       </c>
       <c r="J13">
-        <v>0</v>
+        <v>29</v>
+      </c>
+      <c r="K13" s="1">
+        <v>100</v>
       </c>
     </row>
     <row r="14" spans="1:11">
       <c r="A14" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C14" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="D14">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="E14">
         <v>0</v>
       </c>
       <c r="F14">
-        <v>0</v>
+        <v>26</v>
+      </c>
+      <c r="G14" s="1">
+        <v>0</v>
+      </c>
+      <c r="H14" s="1">
+        <v>100</v>
       </c>
       <c r="J14">
-        <v>0</v>
+        <v>26</v>
+      </c>
+      <c r="K14" s="1">
+        <v>100</v>
       </c>
     </row>
     <row r="15" spans="1:11">
       <c r="A15" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B15" t="s">
+        <v>28</v>
+      </c>
+      <c r="C15" t="s">
+        <v>29</v>
+      </c>
+      <c r="D15">
         <v>25</v>
       </c>
-      <c r="C15" t="s">
-        <v>35</v>
-      </c>
-      <c r="D15">
-        <v>0</v>
-      </c>
       <c r="E15">
         <v>0</v>
       </c>
       <c r="F15">
-        <v>0</v>
+        <v>25</v>
+      </c>
+      <c r="G15" s="1">
+        <v>0</v>
+      </c>
+      <c r="H15" s="1">
+        <v>100</v>
       </c>
       <c r="J15">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11">
-      <c r="A16" t="s">
-        <v>11</v>
-      </c>
-      <c r="B16" t="s">
-        <v>26</v>
-      </c>
-      <c r="C16" t="s">
-        <v>34</v>
-      </c>
-      <c r="D16">
-        <v>0</v>
-      </c>
-      <c r="E16">
-        <v>0</v>
-      </c>
-      <c r="F16">
-        <v>0</v>
-      </c>
-      <c r="J16">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11">
-      <c r="A17" t="s">
-        <v>11</v>
-      </c>
-      <c r="B17" t="s">
-        <v>26</v>
-      </c>
-      <c r="C17" t="s">
-        <v>35</v>
-      </c>
-      <c r="D17">
-        <v>0</v>
-      </c>
-      <c r="E17">
-        <v>0</v>
-      </c>
-      <c r="F17">
-        <v>0</v>
-      </c>
-      <c r="J17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11">
-      <c r="A18" t="s">
-        <v>11</v>
-      </c>
-      <c r="B18" t="s">
-        <v>27</v>
-      </c>
-      <c r="C18" t="s">
-        <v>34</v>
-      </c>
-      <c r="D18">
-        <v>0</v>
-      </c>
-      <c r="E18">
-        <v>0</v>
-      </c>
-      <c r="F18">
-        <v>0</v>
-      </c>
-      <c r="J18">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:11">
-      <c r="A19" t="s">
-        <v>11</v>
-      </c>
-      <c r="B19" t="s">
-        <v>27</v>
-      </c>
-      <c r="C19" t="s">
-        <v>35</v>
-      </c>
-      <c r="D19">
-        <v>0</v>
-      </c>
-      <c r="E19">
-        <v>0</v>
-      </c>
-      <c r="F19">
-        <v>0</v>
-      </c>
-      <c r="J19">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:11">
-      <c r="A20" t="s">
-        <v>11</v>
-      </c>
-      <c r="B20" t="s">
-        <v>28</v>
-      </c>
-      <c r="C20" t="s">
-        <v>34</v>
-      </c>
-      <c r="D20">
-        <v>32</v>
-      </c>
-      <c r="E20">
-        <v>0</v>
-      </c>
-      <c r="F20">
-        <v>32</v>
-      </c>
-      <c r="G20" s="1">
-        <v>0</v>
-      </c>
-      <c r="H20" s="1">
-        <v>100</v>
-      </c>
-      <c r="J20">
-        <v>32</v>
-      </c>
-      <c r="K20" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="21" spans="1:11">
-      <c r="A21" t="s">
-        <v>11</v>
-      </c>
-      <c r="B21" t="s">
-        <v>28</v>
-      </c>
-      <c r="C21" t="s">
-        <v>35</v>
-      </c>
-      <c r="D21">
-        <v>0</v>
-      </c>
-      <c r="E21">
-        <v>0</v>
-      </c>
-      <c r="F21">
-        <v>0</v>
-      </c>
-      <c r="J21">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:11">
-      <c r="A22" t="s">
-        <v>11</v>
-      </c>
-      <c r="B22" t="s">
-        <v>29</v>
-      </c>
-      <c r="C22" t="s">
-        <v>35</v>
-      </c>
-      <c r="D22">
-        <v>0</v>
-      </c>
-      <c r="E22">
-        <v>0</v>
-      </c>
-      <c r="F22">
-        <v>0</v>
-      </c>
-      <c r="J22">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:11">
-      <c r="A23" t="s">
-        <v>12</v>
-      </c>
-      <c r="B23" t="s">
-        <v>30</v>
-      </c>
-      <c r="C23" t="s">
-        <v>33</v>
-      </c>
-      <c r="D23">
-        <v>33</v>
-      </c>
-      <c r="E23">
-        <v>0</v>
-      </c>
-      <c r="F23">
-        <v>33</v>
-      </c>
-      <c r="G23" s="1">
-        <v>0</v>
-      </c>
-      <c r="H23" s="1">
-        <v>100</v>
-      </c>
-      <c r="J23">
-        <v>33</v>
-      </c>
-      <c r="K23" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="24" spans="1:11">
-      <c r="A24" t="s">
-        <v>12</v>
-      </c>
-      <c r="B24" t="s">
-        <v>31</v>
-      </c>
-      <c r="C24" t="s">
-        <v>33</v>
-      </c>
-      <c r="D24">
-        <v>29</v>
-      </c>
-      <c r="E24">
-        <v>0</v>
-      </c>
-      <c r="F24">
-        <v>29</v>
-      </c>
-      <c r="G24" s="1">
-        <v>0</v>
-      </c>
-      <c r="H24" s="1">
-        <v>100</v>
-      </c>
-      <c r="J24">
-        <v>29</v>
-      </c>
-      <c r="K24" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="25" spans="1:11">
-      <c r="A25" t="s">
-        <v>13</v>
-      </c>
-      <c r="B25" t="s">
-        <v>29</v>
-      </c>
-      <c r="C25" t="s">
-        <v>34</v>
-      </c>
-      <c r="D25">
-        <v>26</v>
-      </c>
-      <c r="E25">
-        <v>0</v>
-      </c>
-      <c r="F25">
-        <v>26</v>
-      </c>
-      <c r="G25" s="1">
-        <v>0</v>
-      </c>
-      <c r="H25" s="1">
-        <v>100</v>
-      </c>
-      <c r="J25">
-        <v>26</v>
-      </c>
-      <c r="K25" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="26" spans="1:11">
-      <c r="A26" t="s">
-        <v>14</v>
-      </c>
-      <c r="B26" t="s">
-        <v>32</v>
-      </c>
-      <c r="C26" t="s">
-        <v>33</v>
-      </c>
-      <c r="D26">
         <v>25</v>
       </c>
-      <c r="E26">
-        <v>0</v>
-      </c>
-      <c r="F26">
-        <v>25</v>
-      </c>
-      <c r="G26" s="1">
-        <v>0</v>
-      </c>
-      <c r="H26" s="1">
-        <v>100</v>
-      </c>
-      <c r="J26">
-        <v>25</v>
-      </c>
-      <c r="K26" s="1">
+      <c r="K15" s="1">
         <v>100</v>
       </c>
     </row>
@@ -2023,7 +1511,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K26"/>
+  <dimension ref="A1:K15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -2076,7 +1564,7 @@
         <v>15</v>
       </c>
       <c r="C2" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="D2">
         <v>31</v>
@@ -2111,7 +1599,7 @@
         <v>16</v>
       </c>
       <c r="C3" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="D3">
         <v>41</v>
@@ -2146,7 +1634,7 @@
         <v>17</v>
       </c>
       <c r="C4" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="D4">
         <v>27</v>
@@ -2181,7 +1669,7 @@
         <v>18</v>
       </c>
       <c r="C5" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="D5">
         <v>38</v>
@@ -2216,7 +1704,7 @@
         <v>19</v>
       </c>
       <c r="C6" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="D6">
         <v>28</v>
@@ -2251,7 +1739,7 @@
         <v>20</v>
       </c>
       <c r="C7" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="D7">
         <v>41</v>
@@ -2286,7 +1774,7 @@
         <v>21</v>
       </c>
       <c r="C8" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="D8">
         <v>32</v>
@@ -2321,7 +1809,7 @@
         <v>22</v>
       </c>
       <c r="C9" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="D9">
         <v>14</v>
@@ -2356,18 +1844,30 @@
         <v>23</v>
       </c>
       <c r="C10" t="s">
+        <v>30</v>
+      </c>
+      <c r="D10">
         <v>34</v>
       </c>
-      <c r="D10">
-        <v>0</v>
-      </c>
       <c r="E10">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="F10">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="G10" s="1">
+        <v>97.06</v>
+      </c>
+      <c r="H10" s="1">
+        <v>2.94</v>
+      </c>
+      <c r="I10" s="2">
+        <v>9</v>
       </c>
       <c r="J10">
+        <v>0</v>
+      </c>
+      <c r="K10" s="1">
         <v>0</v>
       </c>
     </row>
@@ -2376,426 +1876,170 @@
         <v>11</v>
       </c>
       <c r="B11" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C11" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="D11">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="E11">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="F11">
         <v>0</v>
       </c>
+      <c r="G11" s="1">
+        <v>100</v>
+      </c>
+      <c r="H11" s="1">
+        <v>0</v>
+      </c>
+      <c r="I11" s="2">
+        <v>9.800000000000001</v>
+      </c>
       <c r="J11">
+        <v>0</v>
+      </c>
+      <c r="K11" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:11">
       <c r="A12" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B12" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C12" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="D12">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E12">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="F12">
+        <v>7</v>
+      </c>
+      <c r="G12" s="1">
+        <v>78.79000000000001</v>
+      </c>
+      <c r="H12" s="1">
+        <v>21.21</v>
+      </c>
+      <c r="I12" s="2">
+        <v>7.2</v>
+      </c>
+      <c r="J12">
         <v>1</v>
       </c>
-      <c r="G12" s="1">
-        <v>97.06</v>
-      </c>
-      <c r="H12" s="1">
-        <v>2.94</v>
-      </c>
-      <c r="I12" s="2">
-        <v>9</v>
-      </c>
-      <c r="J12">
-        <v>0</v>
-      </c>
       <c r="K12" s="1">
-        <v>0</v>
+        <v>3.03</v>
       </c>
     </row>
     <row r="13" spans="1:11">
       <c r="A13" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B13" t="s">
+        <v>26</v>
+      </c>
+      <c r="C13" t="s">
+        <v>29</v>
+      </c>
+      <c r="D13">
+        <v>29</v>
+      </c>
+      <c r="E13">
         <v>24</v>
       </c>
-      <c r="C13" t="s">
-        <v>35</v>
-      </c>
-      <c r="D13">
-        <v>0</v>
-      </c>
-      <c r="E13">
-        <v>0</v>
-      </c>
       <c r="F13">
-        <v>0</v>
+        <v>5</v>
+      </c>
+      <c r="G13" s="1">
+        <v>82.76000000000001</v>
+      </c>
+      <c r="H13" s="1">
+        <v>17.24</v>
+      </c>
+      <c r="I13" s="2">
+        <v>7.1</v>
       </c>
       <c r="J13">
+        <v>0</v>
+      </c>
+      <c r="K13" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:11">
       <c r="A14" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B14" t="s">
+        <v>27</v>
+      </c>
+      <c r="C14" t="s">
+        <v>30</v>
+      </c>
+      <c r="D14">
+        <v>26</v>
+      </c>
+      <c r="E14">
         <v>25</v>
       </c>
-      <c r="C14" t="s">
-        <v>34</v>
-      </c>
-      <c r="D14">
-        <v>0</v>
-      </c>
-      <c r="E14">
-        <v>0</v>
-      </c>
       <c r="F14">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="G14" s="1">
+        <v>96.15000000000001</v>
+      </c>
+      <c r="H14" s="1">
+        <v>3.85</v>
+      </c>
+      <c r="I14" s="2">
+        <v>9.1</v>
       </c>
       <c r="J14">
+        <v>0</v>
+      </c>
+      <c r="K14" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:11">
       <c r="A15" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B15" t="s">
+        <v>28</v>
+      </c>
+      <c r="C15" t="s">
+        <v>29</v>
+      </c>
+      <c r="D15">
         <v>25</v>
       </c>
-      <c r="C15" t="s">
-        <v>35</v>
-      </c>
-      <c r="D15">
-        <v>0</v>
-      </c>
       <c r="E15">
         <v>0</v>
       </c>
       <c r="F15">
-        <v>0</v>
+        <v>25</v>
+      </c>
+      <c r="G15" s="1">
+        <v>0</v>
+      </c>
+      <c r="H15" s="1">
+        <v>100</v>
       </c>
       <c r="J15">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11">
-      <c r="A16" t="s">
-        <v>11</v>
-      </c>
-      <c r="B16" t="s">
-        <v>26</v>
-      </c>
-      <c r="C16" t="s">
-        <v>34</v>
-      </c>
-      <c r="D16">
-        <v>0</v>
-      </c>
-      <c r="E16">
-        <v>0</v>
-      </c>
-      <c r="F16">
-        <v>0</v>
-      </c>
-      <c r="J16">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11">
-      <c r="A17" t="s">
-        <v>11</v>
-      </c>
-      <c r="B17" t="s">
-        <v>26</v>
-      </c>
-      <c r="C17" t="s">
-        <v>35</v>
-      </c>
-      <c r="D17">
-        <v>0</v>
-      </c>
-      <c r="E17">
-        <v>0</v>
-      </c>
-      <c r="F17">
-        <v>0</v>
-      </c>
-      <c r="J17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11">
-      <c r="A18" t="s">
-        <v>11</v>
-      </c>
-      <c r="B18" t="s">
-        <v>27</v>
-      </c>
-      <c r="C18" t="s">
-        <v>34</v>
-      </c>
-      <c r="D18">
-        <v>0</v>
-      </c>
-      <c r="E18">
-        <v>0</v>
-      </c>
-      <c r="F18">
-        <v>0</v>
-      </c>
-      <c r="J18">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:11">
-      <c r="A19" t="s">
-        <v>11</v>
-      </c>
-      <c r="B19" t="s">
-        <v>27</v>
-      </c>
-      <c r="C19" t="s">
-        <v>35</v>
-      </c>
-      <c r="D19">
-        <v>0</v>
-      </c>
-      <c r="E19">
-        <v>0</v>
-      </c>
-      <c r="F19">
-        <v>0</v>
-      </c>
-      <c r="J19">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:11">
-      <c r="A20" t="s">
-        <v>11</v>
-      </c>
-      <c r="B20" t="s">
-        <v>28</v>
-      </c>
-      <c r="C20" t="s">
-        <v>34</v>
-      </c>
-      <c r="D20">
-        <v>32</v>
-      </c>
-      <c r="E20">
-        <v>32</v>
-      </c>
-      <c r="F20">
-        <v>0</v>
-      </c>
-      <c r="G20" s="1">
-        <v>100</v>
-      </c>
-      <c r="H20" s="1">
-        <v>0</v>
-      </c>
-      <c r="I20" s="2">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="J20">
-        <v>0</v>
-      </c>
-      <c r="K20" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:11">
-      <c r="A21" t="s">
-        <v>11</v>
-      </c>
-      <c r="B21" t="s">
-        <v>28</v>
-      </c>
-      <c r="C21" t="s">
-        <v>35</v>
-      </c>
-      <c r="D21">
-        <v>0</v>
-      </c>
-      <c r="E21">
-        <v>0</v>
-      </c>
-      <c r="F21">
-        <v>0</v>
-      </c>
-      <c r="J21">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:11">
-      <c r="A22" t="s">
-        <v>11</v>
-      </c>
-      <c r="B22" t="s">
-        <v>29</v>
-      </c>
-      <c r="C22" t="s">
-        <v>35</v>
-      </c>
-      <c r="D22">
-        <v>0</v>
-      </c>
-      <c r="E22">
-        <v>0</v>
-      </c>
-      <c r="F22">
-        <v>0</v>
-      </c>
-      <c r="J22">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:11">
-      <c r="A23" t="s">
-        <v>12</v>
-      </c>
-      <c r="B23" t="s">
-        <v>30</v>
-      </c>
-      <c r="C23" t="s">
-        <v>33</v>
-      </c>
-      <c r="D23">
-        <v>33</v>
-      </c>
-      <c r="E23">
-        <v>0</v>
-      </c>
-      <c r="F23">
-        <v>33</v>
-      </c>
-      <c r="G23" s="1">
-        <v>0</v>
-      </c>
-      <c r="H23" s="1">
-        <v>100</v>
-      </c>
-      <c r="J23">
-        <v>33</v>
-      </c>
-      <c r="K23" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="24" spans="1:11">
-      <c r="A24" t="s">
-        <v>12</v>
-      </c>
-      <c r="B24" t="s">
-        <v>31</v>
-      </c>
-      <c r="C24" t="s">
-        <v>33</v>
-      </c>
-      <c r="D24">
-        <v>29</v>
-      </c>
-      <c r="E24">
-        <v>0</v>
-      </c>
-      <c r="F24">
-        <v>29</v>
-      </c>
-      <c r="G24" s="1">
-        <v>0</v>
-      </c>
-      <c r="H24" s="1">
-        <v>100</v>
-      </c>
-      <c r="J24">
-        <v>29</v>
-      </c>
-      <c r="K24" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="25" spans="1:11">
-      <c r="A25" t="s">
-        <v>13</v>
-      </c>
-      <c r="B25" t="s">
-        <v>29</v>
-      </c>
-      <c r="C25" t="s">
-        <v>34</v>
-      </c>
-      <c r="D25">
-        <v>26</v>
-      </c>
-      <c r="E25">
-        <v>0</v>
-      </c>
-      <c r="F25">
-        <v>26</v>
-      </c>
-      <c r="G25" s="1">
-        <v>0</v>
-      </c>
-      <c r="H25" s="1">
-        <v>100</v>
-      </c>
-      <c r="J25">
-        <v>26</v>
-      </c>
-      <c r="K25" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="26" spans="1:11">
-      <c r="A26" t="s">
-        <v>14</v>
-      </c>
-      <c r="B26" t="s">
-        <v>32</v>
-      </c>
-      <c r="C26" t="s">
-        <v>33</v>
-      </c>
-      <c r="D26">
         <v>25</v>
       </c>
-      <c r="E26">
-        <v>0</v>
-      </c>
-      <c r="F26">
-        <v>25</v>
-      </c>
-      <c r="G26" s="1">
-        <v>0</v>
-      </c>
-      <c r="H26" s="1">
-        <v>100</v>
-      </c>
-      <c r="J26">
-        <v>25</v>
-      </c>
-      <c r="K26" s="1">
+      <c r="K15" s="1">
         <v>100</v>
       </c>
     </row>

--- a/academias/Biología - Estadisticos 20222.xlsx
+++ b/academias/Biología - Estadisticos 20222.xlsx
@@ -986,22 +986,25 @@
         <v>25</v>
       </c>
       <c r="E15">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="F15">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="G15" s="1">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="H15" s="1">
-        <v>100</v>
+        <v>64</v>
+      </c>
+      <c r="I15" s="2">
+        <v>5.7</v>
       </c>
       <c r="J15">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="K15" s="1">
-        <v>100</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -2025,22 +2028,25 @@
         <v>25</v>
       </c>
       <c r="E15">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="F15">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="G15" s="1">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="H15" s="1">
-        <v>100</v>
+        <v>64</v>
+      </c>
+      <c r="I15" s="2">
+        <v>6.1</v>
       </c>
       <c r="J15">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="K15" s="1">
-        <v>100</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>

--- a/academias/Biología - Estadisticos 20222.xlsx
+++ b/academias/Biología - Estadisticos 20222.xlsx
@@ -878,28 +878,28 @@
         <v>29</v>
       </c>
       <c r="D12">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E12">
         <v>26</v>
       </c>
       <c r="F12">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G12" s="1">
-        <v>78.79000000000001</v>
+        <v>76.47</v>
       </c>
       <c r="H12" s="1">
-        <v>21.21</v>
+        <v>23.53</v>
       </c>
       <c r="I12" s="2">
-        <v>7.2</v>
+        <v>7.1</v>
       </c>
       <c r="J12">
         <v>1</v>
       </c>
       <c r="K12" s="1">
-        <v>3.03</v>
+        <v>2.94</v>
       </c>
     </row>
     <row r="13" spans="1:11">
@@ -913,28 +913,28 @@
         <v>29</v>
       </c>
       <c r="D13">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E13">
         <v>24</v>
       </c>
       <c r="F13">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G13" s="1">
-        <v>82.76000000000001</v>
+        <v>80</v>
       </c>
       <c r="H13" s="1">
-        <v>17.24</v>
+        <v>20</v>
       </c>
       <c r="I13" s="2">
         <v>7.1</v>
       </c>
       <c r="J13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K13" s="1">
-        <v>0</v>
+        <v>3.33</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -1001,10 +1001,10 @@
         <v>5.7</v>
       </c>
       <c r="J15">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K15" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1390,13 +1390,13 @@
         <v>29</v>
       </c>
       <c r="D12">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E12">
         <v>0</v>
       </c>
       <c r="F12">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G12" s="1">
         <v>0</v>
@@ -1405,7 +1405,7 @@
         <v>100</v>
       </c>
       <c r="J12">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K12" s="1">
         <v>100</v>
@@ -1422,13 +1422,13 @@
         <v>29</v>
       </c>
       <c r="D13">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E13">
         <v>0</v>
       </c>
       <c r="F13">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G13" s="1">
         <v>0</v>
@@ -1437,7 +1437,7 @@
         <v>100</v>
       </c>
       <c r="J13">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K13" s="1">
         <v>100</v>
@@ -1920,28 +1920,28 @@
         <v>29</v>
       </c>
       <c r="D12">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E12">
         <v>26</v>
       </c>
       <c r="F12">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G12" s="1">
-        <v>78.79000000000001</v>
+        <v>76.47</v>
       </c>
       <c r="H12" s="1">
-        <v>21.21</v>
+        <v>23.53</v>
       </c>
       <c r="I12" s="2">
-        <v>7.2</v>
+        <v>7.1</v>
       </c>
       <c r="J12">
         <v>1</v>
       </c>
       <c r="K12" s="1">
-        <v>3.03</v>
+        <v>2.94</v>
       </c>
     </row>
     <row r="13" spans="1:11">
@@ -1955,28 +1955,28 @@
         <v>29</v>
       </c>
       <c r="D13">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E13">
         <v>24</v>
       </c>
       <c r="F13">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G13" s="1">
-        <v>82.76000000000001</v>
+        <v>80</v>
       </c>
       <c r="H13" s="1">
-        <v>17.24</v>
+        <v>20</v>
       </c>
       <c r="I13" s="2">
         <v>7.1</v>
       </c>
       <c r="J13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K13" s="1">
-        <v>0</v>
+        <v>3.33</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -2043,10 +2043,10 @@
         <v>6.1</v>
       </c>
       <c r="J15">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K15" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/academias/Biología - Estadisticos 20222.xlsx
+++ b/academias/Biología - Estadisticos 20222.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="33">
   <si>
     <t>Docente</t>
   </si>
@@ -51,7 +51,7 @@
     <t>Por_Blan</t>
   </si>
   <si>
-    <t>Desc Desc Desc</t>
+    <t>Barañon Samaniego Graciela de los Ángeles</t>
   </si>
   <si>
     <t>Gomez Lopez Javier</t>
@@ -60,46 +60,52 @@
     <t>Martínez Castillo Columba</t>
   </si>
   <si>
+    <t>Rivera Cruz Ezequiel</t>
+  </si>
+  <si>
+    <t>Vargas Olvera Francisco Eduardo</t>
+  </si>
+  <si>
     <t>Villanueva Morales Luis Arturo</t>
   </si>
   <si>
+    <t>4ARHM</t>
+  </si>
+  <si>
+    <t>4AEV</t>
+  </si>
+  <si>
+    <t>4ALCV</t>
+  </si>
+  <si>
+    <t>4ARHV</t>
+  </si>
+  <si>
+    <t>6ALCV</t>
+  </si>
+  <si>
     <t>4AEM</t>
   </si>
   <si>
+    <t>4BEM</t>
+  </si>
+  <si>
+    <t>6ALCM</t>
+  </si>
+  <si>
+    <t>6BLCM</t>
+  </si>
+  <si>
     <t>4ALCM</t>
   </si>
   <si>
     <t>4APM</t>
   </si>
   <si>
-    <t>4ARHM</t>
-  </si>
-  <si>
-    <t>4BEM</t>
-  </si>
-  <si>
     <t>4BLCM</t>
   </si>
   <si>
-    <t>4AEV</t>
-  </si>
-  <si>
     <t>4ASV</t>
-  </si>
-  <si>
-    <t>6ALCM</t>
-  </si>
-  <si>
-    <t>6BLCM</t>
-  </si>
-  <si>
-    <t>4ALCV</t>
-  </si>
-  <si>
-    <t>4ARHV</t>
-  </si>
-  <si>
-    <t>6ALCV</t>
   </si>
   <si>
     <t>4APV</t>
@@ -522,28 +528,28 @@
         <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C2" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D2">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="E2">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="F2">
         <v>6</v>
       </c>
       <c r="G2" s="1">
-        <v>80.65000000000001</v>
+        <v>84.20999999999999</v>
       </c>
       <c r="H2" s="1">
-        <v>19.35</v>
+        <v>15.79</v>
       </c>
       <c r="I2" s="2">
-        <v>7.9</v>
+        <v>7.7</v>
       </c>
       <c r="J2">
         <v>0</v>
@@ -557,28 +563,28 @@
         <v>11</v>
       </c>
       <c r="B3" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C3" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D3">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="E3">
-        <v>41</v>
+        <v>23</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G3" s="1">
-        <v>100</v>
+        <v>71.88</v>
       </c>
       <c r="H3" s="1">
-        <v>0</v>
+        <v>28.13</v>
       </c>
       <c r="I3" s="2">
-        <v>9.300000000000001</v>
+        <v>6.5</v>
       </c>
       <c r="J3">
         <v>0</v>
@@ -589,101 +595,101 @@
     </row>
     <row r="4" spans="1:11">
       <c r="A4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B4" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C4" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D4">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="E4">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F4">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="G4" s="1">
-        <v>92.59</v>
+        <v>76.47</v>
       </c>
       <c r="H4" s="1">
-        <v>7.41</v>
+        <v>23.53</v>
       </c>
       <c r="I4" s="2">
-        <v>8.699999999999999</v>
+        <v>7.1</v>
       </c>
       <c r="J4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K4" s="1">
-        <v>0</v>
+        <v>2.94</v>
       </c>
     </row>
     <row r="5" spans="1:11">
       <c r="A5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B5" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C5" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D5">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="E5">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="F5">
         <v>6</v>
       </c>
       <c r="G5" s="1">
-        <v>84.20999999999999</v>
+        <v>80</v>
       </c>
       <c r="H5" s="1">
-        <v>15.79</v>
+        <v>20</v>
       </c>
       <c r="I5" s="2">
-        <v>7.7</v>
+        <v>7.1</v>
       </c>
       <c r="J5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K5" s="1">
-        <v>0</v>
+        <v>3.33</v>
       </c>
     </row>
     <row r="6" spans="1:11">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B6" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C6" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="D6">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E6">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="F6">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="G6" s="1">
-        <v>71.43000000000001</v>
+        <v>96.15000000000001</v>
       </c>
       <c r="H6" s="1">
-        <v>28.57</v>
+        <v>3.85</v>
       </c>
       <c r="I6" s="2">
-        <v>8.1</v>
+        <v>9.1</v>
       </c>
       <c r="J6">
         <v>0</v>
@@ -694,31 +700,31 @@
     </row>
     <row r="7" spans="1:11">
       <c r="A7" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B7" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C7" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D7">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="E7">
-        <v>39</v>
+        <v>25</v>
       </c>
       <c r="F7">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G7" s="1">
-        <v>95.12</v>
+        <v>80.65000000000001</v>
       </c>
       <c r="H7" s="1">
-        <v>4.88</v>
+        <v>19.35</v>
       </c>
       <c r="I7" s="2">
-        <v>8.699999999999999</v>
+        <v>7.9</v>
       </c>
       <c r="J7">
         <v>0</v>
@@ -729,31 +735,31 @@
     </row>
     <row r="8" spans="1:11">
       <c r="A8" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B8" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C8" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D8">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="E8">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="F8">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G8" s="1">
-        <v>71.88</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="H8" s="1">
-        <v>28.13</v>
+        <v>28.57</v>
       </c>
       <c r="I8" s="2">
-        <v>6.5</v>
+        <v>8.1</v>
       </c>
       <c r="J8">
         <v>0</v>
@@ -764,31 +770,31 @@
     </row>
     <row r="9" spans="1:11">
       <c r="A9" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B9" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C9" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="D9">
-        <v>14</v>
+        <v>34</v>
       </c>
       <c r="E9">
-        <v>8</v>
+        <v>33</v>
       </c>
       <c r="F9">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G9" s="1">
-        <v>57.14</v>
+        <v>97.06</v>
       </c>
       <c r="H9" s="1">
-        <v>42.86</v>
+        <v>2.94</v>
       </c>
       <c r="I9" s="2">
-        <v>6.6</v>
+        <v>9</v>
       </c>
       <c r="J9">
         <v>0</v>
@@ -799,31 +805,31 @@
     </row>
     <row r="10" spans="1:11">
       <c r="A10" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B10" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C10" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D10">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E10">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G10" s="1">
-        <v>97.06</v>
+        <v>100</v>
       </c>
       <c r="H10" s="1">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="I10" s="2">
-        <v>9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J10">
         <v>0</v>
@@ -834,19 +840,19 @@
     </row>
     <row r="11" spans="1:11">
       <c r="A11" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="B11" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C11" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D11">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="E11">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="F11">
         <v>0</v>
@@ -858,7 +864,7 @@
         <v>0</v>
       </c>
       <c r="I11" s="2">
-        <v>9.800000000000001</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J11">
         <v>0</v>
@@ -869,101 +875,101 @@
     </row>
     <row r="12" spans="1:11">
       <c r="A12" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B12" t="s">
+        <v>27</v>
+      </c>
+      <c r="C12" t="s">
+        <v>31</v>
+      </c>
+      <c r="D12">
+        <v>27</v>
+      </c>
+      <c r="E12">
         <v>25</v>
       </c>
-      <c r="C12" t="s">
-        <v>29</v>
-      </c>
-      <c r="D12">
-        <v>34</v>
-      </c>
-      <c r="E12">
-        <v>26</v>
-      </c>
       <c r="F12">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="G12" s="1">
-        <v>76.47</v>
+        <v>92.59</v>
       </c>
       <c r="H12" s="1">
-        <v>23.53</v>
+        <v>7.41</v>
       </c>
       <c r="I12" s="2">
-        <v>7.1</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K12" s="1">
-        <v>2.94</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:11">
       <c r="A13" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B13" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C13" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D13">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="E13">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="F13">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G13" s="1">
-        <v>80</v>
+        <v>95.12</v>
       </c>
       <c r="H13" s="1">
-        <v>20</v>
+        <v>4.88</v>
       </c>
       <c r="I13" s="2">
-        <v>7.1</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K13" s="1">
-        <v>3.33</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:11">
       <c r="A14" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B14" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C14" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D14">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="E14">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="F14">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G14" s="1">
-        <v>96.15000000000001</v>
+        <v>57.14</v>
       </c>
       <c r="H14" s="1">
-        <v>3.85</v>
+        <v>42.86</v>
       </c>
       <c r="I14" s="2">
-        <v>9.1</v>
+        <v>6.6</v>
       </c>
       <c r="J14">
         <v>0</v>
@@ -974,13 +980,13 @@
     </row>
     <row r="15" spans="1:11">
       <c r="A15" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B15" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C15" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D15">
         <v>25</v>
@@ -1064,19 +1070,19 @@
         <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C2" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D2">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="G2" s="1">
         <v>0</v>
@@ -1085,7 +1091,7 @@
         <v>100</v>
       </c>
       <c r="J2">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="K2" s="1">
         <v>100</v>
@@ -1096,19 +1102,19 @@
         <v>11</v>
       </c>
       <c r="B3" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C3" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D3">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="E3">
         <v>0</v>
       </c>
       <c r="F3">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="G3" s="1">
         <v>0</v>
@@ -1117,7 +1123,7 @@
         <v>100</v>
       </c>
       <c r="J3">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="K3" s="1">
         <v>100</v>
@@ -1125,22 +1131,22 @@
     </row>
     <row r="4" spans="1:11">
       <c r="A4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B4" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C4" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D4">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="E4">
         <v>0</v>
       </c>
       <c r="F4">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="G4" s="1">
         <v>0</v>
@@ -1149,7 +1155,7 @@
         <v>100</v>
       </c>
       <c r="J4">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="K4" s="1">
         <v>100</v>
@@ -1157,22 +1163,22 @@
     </row>
     <row r="5" spans="1:11">
       <c r="A5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B5" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C5" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D5">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="E5">
         <v>0</v>
       </c>
       <c r="F5">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="G5" s="1">
         <v>0</v>
@@ -1181,7 +1187,7 @@
         <v>100</v>
       </c>
       <c r="J5">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="K5" s="1">
         <v>100</v>
@@ -1189,22 +1195,22 @@
     </row>
     <row r="6" spans="1:11">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B6" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C6" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="D6">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E6">
         <v>0</v>
       </c>
       <c r="F6">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G6" s="1">
         <v>0</v>
@@ -1213,7 +1219,7 @@
         <v>100</v>
       </c>
       <c r="J6">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="K6" s="1">
         <v>100</v>
@@ -1221,22 +1227,22 @@
     </row>
     <row r="7" spans="1:11">
       <c r="A7" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B7" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C7" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D7">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="E7">
         <v>0</v>
       </c>
       <c r="F7">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="G7" s="1">
         <v>0</v>
@@ -1245,7 +1251,7 @@
         <v>100</v>
       </c>
       <c r="J7">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="K7" s="1">
         <v>100</v>
@@ -1253,22 +1259,22 @@
     </row>
     <row r="8" spans="1:11">
       <c r="A8" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B8" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C8" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D8">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="E8">
         <v>0</v>
       </c>
       <c r="F8">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="G8" s="1">
         <v>0</v>
@@ -1277,7 +1283,7 @@
         <v>100</v>
       </c>
       <c r="J8">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="K8" s="1">
         <v>100</v>
@@ -1285,22 +1291,22 @@
     </row>
     <row r="9" spans="1:11">
       <c r="A9" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B9" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C9" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="D9">
-        <v>14</v>
+        <v>34</v>
       </c>
       <c r="E9">
         <v>0</v>
       </c>
       <c r="F9">
-        <v>14</v>
+        <v>34</v>
       </c>
       <c r="G9" s="1">
         <v>0</v>
@@ -1309,7 +1315,7 @@
         <v>100</v>
       </c>
       <c r="J9">
-        <v>14</v>
+        <v>34</v>
       </c>
       <c r="K9" s="1">
         <v>100</v>
@@ -1317,22 +1323,22 @@
     </row>
     <row r="10" spans="1:11">
       <c r="A10" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B10" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C10" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D10">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E10">
         <v>0</v>
       </c>
       <c r="F10">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="G10" s="1">
         <v>0</v>
@@ -1341,7 +1347,7 @@
         <v>100</v>
       </c>
       <c r="J10">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="K10" s="1">
         <v>100</v>
@@ -1349,22 +1355,22 @@
     </row>
     <row r="11" spans="1:11">
       <c r="A11" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="B11" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C11" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D11">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="E11">
         <v>0</v>
       </c>
       <c r="F11">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="G11" s="1">
         <v>0</v>
@@ -1373,7 +1379,7 @@
         <v>100</v>
       </c>
       <c r="J11">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="K11" s="1">
         <v>100</v>
@@ -1381,22 +1387,22 @@
     </row>
     <row r="12" spans="1:11">
       <c r="A12" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B12" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C12" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D12">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="E12">
         <v>0</v>
       </c>
       <c r="F12">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="G12" s="1">
         <v>0</v>
@@ -1405,7 +1411,7 @@
         <v>100</v>
       </c>
       <c r="J12">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="K12" s="1">
         <v>100</v>
@@ -1413,22 +1419,22 @@
     </row>
     <row r="13" spans="1:11">
       <c r="A13" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B13" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C13" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D13">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="E13">
         <v>0</v>
       </c>
       <c r="F13">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="G13" s="1">
         <v>0</v>
@@ -1437,7 +1443,7 @@
         <v>100</v>
       </c>
       <c r="J13">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="K13" s="1">
         <v>100</v>
@@ -1445,22 +1451,22 @@
     </row>
     <row r="14" spans="1:11">
       <c r="A14" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B14" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C14" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D14">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="E14">
         <v>0</v>
       </c>
       <c r="F14">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="G14" s="1">
         <v>0</v>
@@ -1469,7 +1475,7 @@
         <v>100</v>
       </c>
       <c r="J14">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="K14" s="1">
         <v>100</v>
@@ -1477,13 +1483,13 @@
     </row>
     <row r="15" spans="1:11">
       <c r="A15" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B15" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C15" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D15">
         <v>25</v>
@@ -1564,28 +1570,28 @@
         <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C2" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D2">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="E2">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="F2">
         <v>6</v>
       </c>
       <c r="G2" s="1">
-        <v>80.65000000000001</v>
+        <v>84.20999999999999</v>
       </c>
       <c r="H2" s="1">
-        <v>19.35</v>
+        <v>15.79</v>
       </c>
       <c r="I2" s="2">
-        <v>7.9</v>
+        <v>7.7</v>
       </c>
       <c r="J2">
         <v>0</v>
@@ -1599,28 +1605,28 @@
         <v>11</v>
       </c>
       <c r="B3" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C3" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D3">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="E3">
-        <v>41</v>
+        <v>23</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G3" s="1">
-        <v>100</v>
+        <v>71.88</v>
       </c>
       <c r="H3" s="1">
-        <v>0</v>
+        <v>28.13</v>
       </c>
       <c r="I3" s="2">
-        <v>9.300000000000001</v>
+        <v>6.5</v>
       </c>
       <c r="J3">
         <v>0</v>
@@ -1631,101 +1637,101 @@
     </row>
     <row r="4" spans="1:11">
       <c r="A4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B4" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C4" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D4">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="E4">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F4">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="G4" s="1">
-        <v>92.59</v>
+        <v>76.47</v>
       </c>
       <c r="H4" s="1">
-        <v>7.41</v>
+        <v>23.53</v>
       </c>
       <c r="I4" s="2">
-        <v>8.699999999999999</v>
+        <v>7.1</v>
       </c>
       <c r="J4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K4" s="1">
-        <v>0</v>
+        <v>2.94</v>
       </c>
     </row>
     <row r="5" spans="1:11">
       <c r="A5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B5" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C5" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D5">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="E5">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="F5">
         <v>6</v>
       </c>
       <c r="G5" s="1">
-        <v>84.20999999999999</v>
+        <v>80</v>
       </c>
       <c r="H5" s="1">
-        <v>15.79</v>
+        <v>20</v>
       </c>
       <c r="I5" s="2">
-        <v>7.7</v>
+        <v>7.1</v>
       </c>
       <c r="J5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K5" s="1">
-        <v>0</v>
+        <v>3.33</v>
       </c>
     </row>
     <row r="6" spans="1:11">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B6" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C6" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="D6">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E6">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="F6">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="G6" s="1">
-        <v>71.43000000000001</v>
+        <v>96.15000000000001</v>
       </c>
       <c r="H6" s="1">
-        <v>28.57</v>
+        <v>3.85</v>
       </c>
       <c r="I6" s="2">
-        <v>8.1</v>
+        <v>9.1</v>
       </c>
       <c r="J6">
         <v>0</v>
@@ -1736,31 +1742,31 @@
     </row>
     <row r="7" spans="1:11">
       <c r="A7" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B7" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C7" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D7">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="E7">
-        <v>39</v>
+        <v>25</v>
       </c>
       <c r="F7">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G7" s="1">
-        <v>95.12</v>
+        <v>80.65000000000001</v>
       </c>
       <c r="H7" s="1">
-        <v>4.88</v>
+        <v>19.35</v>
       </c>
       <c r="I7" s="2">
-        <v>8.699999999999999</v>
+        <v>7.9</v>
       </c>
       <c r="J7">
         <v>0</v>
@@ -1771,31 +1777,31 @@
     </row>
     <row r="8" spans="1:11">
       <c r="A8" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B8" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C8" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D8">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="E8">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="F8">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G8" s="1">
-        <v>71.88</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="H8" s="1">
-        <v>28.13</v>
+        <v>28.57</v>
       </c>
       <c r="I8" s="2">
-        <v>6.5</v>
+        <v>8.1</v>
       </c>
       <c r="J8">
         <v>0</v>
@@ -1806,31 +1812,31 @@
     </row>
     <row r="9" spans="1:11">
       <c r="A9" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B9" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C9" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="D9">
-        <v>14</v>
+        <v>34</v>
       </c>
       <c r="E9">
-        <v>8</v>
+        <v>33</v>
       </c>
       <c r="F9">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G9" s="1">
-        <v>57.14</v>
+        <v>97.06</v>
       </c>
       <c r="H9" s="1">
-        <v>42.86</v>
+        <v>2.94</v>
       </c>
       <c r="I9" s="2">
-        <v>6.6</v>
+        <v>9</v>
       </c>
       <c r="J9">
         <v>0</v>
@@ -1841,31 +1847,31 @@
     </row>
     <row r="10" spans="1:11">
       <c r="A10" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B10" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C10" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D10">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E10">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G10" s="1">
-        <v>97.06</v>
+        <v>100</v>
       </c>
       <c r="H10" s="1">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="I10" s="2">
-        <v>9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J10">
         <v>0</v>
@@ -1876,19 +1882,19 @@
     </row>
     <row r="11" spans="1:11">
       <c r="A11" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="B11" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C11" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D11">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="E11">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="F11">
         <v>0</v>
@@ -1900,7 +1906,7 @@
         <v>0</v>
       </c>
       <c r="I11" s="2">
-        <v>9.800000000000001</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J11">
         <v>0</v>
@@ -1911,101 +1917,101 @@
     </row>
     <row r="12" spans="1:11">
       <c r="A12" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B12" t="s">
+        <v>27</v>
+      </c>
+      <c r="C12" t="s">
+        <v>31</v>
+      </c>
+      <c r="D12">
+        <v>27</v>
+      </c>
+      <c r="E12">
         <v>25</v>
       </c>
-      <c r="C12" t="s">
-        <v>29</v>
-      </c>
-      <c r="D12">
-        <v>34</v>
-      </c>
-      <c r="E12">
-        <v>26</v>
-      </c>
       <c r="F12">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="G12" s="1">
-        <v>76.47</v>
+        <v>92.59</v>
       </c>
       <c r="H12" s="1">
-        <v>23.53</v>
+        <v>7.41</v>
       </c>
       <c r="I12" s="2">
-        <v>7.1</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K12" s="1">
-        <v>2.94</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:11">
       <c r="A13" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B13" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C13" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D13">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="E13">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="F13">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G13" s="1">
-        <v>80</v>
+        <v>95.12</v>
       </c>
       <c r="H13" s="1">
-        <v>20</v>
+        <v>4.88</v>
       </c>
       <c r="I13" s="2">
-        <v>7.1</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K13" s="1">
-        <v>3.33</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:11">
       <c r="A14" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B14" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C14" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D14">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="E14">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="F14">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G14" s="1">
-        <v>96.15000000000001</v>
+        <v>57.14</v>
       </c>
       <c r="H14" s="1">
-        <v>3.85</v>
+        <v>42.86</v>
       </c>
       <c r="I14" s="2">
-        <v>9.1</v>
+        <v>6.6</v>
       </c>
       <c r="J14">
         <v>0</v>
@@ -2016,13 +2022,13 @@
     </row>
     <row r="15" spans="1:11">
       <c r="A15" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B15" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C15" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D15">
         <v>25</v>

--- a/academias/Biología - Estadisticos 20222.xlsx
+++ b/academias/Biología - Estadisticos 20222.xlsx
@@ -8,25 +8,24 @@
   </bookViews>
   <sheets>
     <sheet name="1er Parcial" sheetId="1" r:id="rId1"/>
-    <sheet name="2o Parcial" sheetId="2" r:id="rId2"/>
-    <sheet name="Final" sheetId="3" r:id="rId3"/>
+    <sheet name="Final" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="34">
   <si>
     <t>Docente</t>
   </si>
   <si>
+    <t>Mat</t>
+  </si>
+  <si>
     <t>Grupo</t>
   </si>
   <si>
-    <t>Mat</t>
-  </si>
-  <si>
     <t>Totales</t>
   </si>
   <si>
@@ -36,10 +35,10 @@
     <t>Reprobados</t>
   </si>
   <si>
-    <t>Por_Apro</t>
-  </si>
-  <si>
-    <t>Por_Repro</t>
+    <t>por_aprobados</t>
+  </si>
+  <si>
+    <t>por_reprobados</t>
   </si>
   <si>
     <t>Promedio</t>
@@ -48,7 +47,7 @@
     <t>Blancos</t>
   </si>
   <si>
-    <t>Por_Blan</t>
+    <t>por_blancos</t>
   </si>
   <si>
     <t>Barañon Samaniego Graciela de los Ángeles</t>
@@ -63,12 +62,21 @@
     <t>Rivera Cruz Ezequiel</t>
   </si>
   <si>
+    <t>Total</t>
+  </si>
+  <si>
     <t>Vargas Olvera Francisco Eduardo</t>
   </si>
   <si>
     <t>Villanueva Morales Luis Arturo</t>
   </si>
   <si>
+    <t>ECOLOGÍA</t>
+  </si>
+  <si>
+    <t>TEMAS DE BIOLOGÍA CONTEMPORÁNEA</t>
+  </si>
+  <si>
     <t>4ARHM</t>
   </si>
   <si>
@@ -109,12 +117,6 @@
   </si>
   <si>
     <t>4APV</t>
-  </si>
-  <si>
-    <t>ECOLOGÍA</t>
-  </si>
-  <si>
-    <t>TEMAS DE BIOLOGÍA CONTEMPORÁNEA</t>
   </si>
 </sst>
 </file>
@@ -478,11 +480,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K15"/>
+  <dimension ref="A1:K22"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
-    <col min="3" max="3" width="30.7109375" customWidth="1"/>
+    <col min="2" max="2" width="30.7109375" customWidth="1"/>
     <col min="7" max="8" width="9.140625" style="1"/>
     <col min="9" max="9" width="9.140625" style="2"/>
     <col min="11" max="11" width="9.140625" style="1"/>
@@ -528,10 +530,10 @@
         <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C2" t="s">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="D2">
         <v>38</v>
@@ -543,10 +545,10 @@
         <v>6</v>
       </c>
       <c r="G2" s="1">
-        <v>84.20999999999999</v>
+        <v>84.2</v>
       </c>
       <c r="H2" s="1">
-        <v>15.79</v>
+        <v>15.8</v>
       </c>
       <c r="I2" s="2">
         <v>7.7</v>
@@ -566,7 +568,7 @@
         <v>18</v>
       </c>
       <c r="C3" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="D3">
         <v>32</v>
@@ -578,10 +580,10 @@
         <v>9</v>
       </c>
       <c r="G3" s="1">
-        <v>71.88</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="H3" s="1">
-        <v>28.13</v>
+        <v>28.1</v>
       </c>
       <c r="I3" s="2">
         <v>6.5</v>
@@ -595,37 +597,31 @@
     </row>
     <row r="4" spans="1:11">
       <c r="A4" t="s">
-        <v>12</v>
-      </c>
-      <c r="B4" t="s">
-        <v>19</v>
-      </c>
-      <c r="C4" t="s">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="D4">
-        <v>34</v>
+        <v>70</v>
       </c>
       <c r="E4">
-        <v>26</v>
+        <v>55</v>
       </c>
       <c r="F4">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="G4" s="1">
-        <v>76.47</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="H4" s="1">
-        <v>23.53</v>
+        <v>21.4</v>
       </c>
       <c r="I4" s="2">
         <v>7.1</v>
       </c>
       <c r="J4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K4" s="1">
-        <v>2.94</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -633,25 +629,25 @@
         <v>12</v>
       </c>
       <c r="B5" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C5" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="D5">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="E5">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F5">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G5" s="1">
-        <v>80</v>
+        <v>76.5</v>
       </c>
       <c r="H5" s="1">
-        <v>20</v>
+        <v>23.5</v>
       </c>
       <c r="I5" s="2">
         <v>7.1</v>
@@ -660,106 +656,100 @@
         <v>1</v>
       </c>
       <c r="K5" s="1">
-        <v>3.33</v>
+        <v>2.94</v>
       </c>
     </row>
     <row r="6" spans="1:11">
       <c r="A6" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B6" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C6" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="D6">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="E6">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F6">
+        <v>6</v>
+      </c>
+      <c r="G6" s="1">
+        <v>80</v>
+      </c>
+      <c r="H6" s="1">
+        <v>20</v>
+      </c>
+      <c r="I6" s="2">
+        <v>7.1</v>
+      </c>
+      <c r="J6">
         <v>1</v>
       </c>
-      <c r="G6" s="1">
-        <v>96.15000000000001</v>
-      </c>
-      <c r="H6" s="1">
-        <v>3.85</v>
-      </c>
-      <c r="I6" s="2">
-        <v>9.1</v>
-      </c>
-      <c r="J6">
-        <v>0</v>
-      </c>
       <c r="K6" s="1">
-        <v>0</v>
+        <v>3.33</v>
       </c>
     </row>
     <row r="7" spans="1:11">
       <c r="A7" t="s">
+        <v>12</v>
+      </c>
+      <c r="D7">
+        <v>64</v>
+      </c>
+      <c r="E7">
+        <v>50</v>
+      </c>
+      <c r="F7">
         <v>14</v>
       </c>
-      <c r="B7" t="s">
-        <v>22</v>
-      </c>
-      <c r="C7" t="s">
-        <v>31</v>
-      </c>
-      <c r="D7">
-        <v>31</v>
-      </c>
-      <c r="E7">
-        <v>25</v>
-      </c>
-      <c r="F7">
-        <v>6</v>
-      </c>
       <c r="G7" s="1">
-        <v>80.65000000000001</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="H7" s="1">
-        <v>19.35</v>
+        <v>21.9</v>
       </c>
       <c r="I7" s="2">
-        <v>7.9</v>
+        <v>7.1</v>
       </c>
       <c r="J7">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K7" s="1">
-        <v>0</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="8" spans="1:11">
       <c r="A8" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B8" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="C8" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="D8">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E8">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="F8">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="G8" s="1">
-        <v>71.43000000000001</v>
+        <v>96.2</v>
       </c>
       <c r="H8" s="1">
-        <v>28.57</v>
+        <v>3.8</v>
       </c>
       <c r="I8" s="2">
-        <v>8.1</v>
+        <v>9.1</v>
       </c>
       <c r="J8">
         <v>0</v>
@@ -770,31 +760,25 @@
     </row>
     <row r="9" spans="1:11">
       <c r="A9" t="s">
-        <v>14</v>
-      </c>
-      <c r="B9" t="s">
-        <v>24</v>
-      </c>
-      <c r="C9" t="s">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="D9">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="E9">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="F9">
         <v>1</v>
       </c>
       <c r="G9" s="1">
-        <v>97.06</v>
+        <v>96.2</v>
       </c>
       <c r="H9" s="1">
-        <v>2.94</v>
+        <v>3.8</v>
       </c>
       <c r="I9" s="2">
-        <v>9</v>
+        <v>9.1</v>
       </c>
       <c r="J9">
         <v>0</v>
@@ -808,28 +792,28 @@
         <v>14</v>
       </c>
       <c r="B10" t="s">
+        <v>18</v>
+      </c>
+      <c r="C10" t="s">
         <v>25</v>
       </c>
-      <c r="C10" t="s">
-        <v>32</v>
-      </c>
       <c r="D10">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E10">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="F10">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G10" s="1">
-        <v>100</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="H10" s="1">
-        <v>0</v>
+        <v>19.4</v>
       </c>
       <c r="I10" s="2">
-        <v>9.800000000000001</v>
+        <v>7.9</v>
       </c>
       <c r="J10">
         <v>0</v>
@@ -840,31 +824,31 @@
     </row>
     <row r="11" spans="1:11">
       <c r="A11" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B11" t="s">
+        <v>18</v>
+      </c>
+      <c r="C11" t="s">
         <v>26</v>
       </c>
-      <c r="C11" t="s">
-        <v>31</v>
-      </c>
       <c r="D11">
-        <v>41</v>
+        <v>28</v>
       </c>
       <c r="E11">
-        <v>41</v>
+        <v>20</v>
       </c>
       <c r="F11">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G11" s="1">
-        <v>100</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="H11" s="1">
-        <v>0</v>
+        <v>28.6</v>
       </c>
       <c r="I11" s="2">
-        <v>9.300000000000001</v>
+        <v>8.1</v>
       </c>
       <c r="J11">
         <v>0</v>
@@ -875,31 +859,31 @@
     </row>
     <row r="12" spans="1:11">
       <c r="A12" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B12" t="s">
+        <v>19</v>
+      </c>
+      <c r="C12" t="s">
         <v>27</v>
       </c>
-      <c r="C12" t="s">
-        <v>31</v>
-      </c>
       <c r="D12">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="E12">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="F12">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G12" s="1">
-        <v>92.59</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="H12" s="1">
-        <v>7.41</v>
+        <v>2.9</v>
       </c>
       <c r="I12" s="2">
-        <v>8.699999999999999</v>
+        <v>9</v>
       </c>
       <c r="J12">
         <v>0</v>
@@ -910,31 +894,31 @@
     </row>
     <row r="13" spans="1:11">
       <c r="A13" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C13" t="s">
         <v>28</v>
       </c>
-      <c r="C13" t="s">
-        <v>31</v>
-      </c>
       <c r="D13">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="E13">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="F13">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G13" s="1">
-        <v>95.12</v>
+        <v>100</v>
       </c>
       <c r="H13" s="1">
-        <v>4.88</v>
+        <v>0</v>
       </c>
       <c r="I13" s="2">
-        <v>8.699999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J13">
         <v>0</v>
@@ -945,31 +929,25 @@
     </row>
     <row r="14" spans="1:11">
       <c r="A14" t="s">
+        <v>14</v>
+      </c>
+      <c r="D14">
+        <v>125</v>
+      </c>
+      <c r="E14">
+        <v>110</v>
+      </c>
+      <c r="F14">
         <v>15</v>
       </c>
-      <c r="B14" t="s">
-        <v>29</v>
-      </c>
-      <c r="C14" t="s">
-        <v>31</v>
-      </c>
-      <c r="D14">
-        <v>14</v>
-      </c>
-      <c r="E14">
-        <v>8</v>
-      </c>
-      <c r="F14">
-        <v>6</v>
-      </c>
       <c r="G14" s="1">
-        <v>57.14</v>
+        <v>88</v>
       </c>
       <c r="H14" s="1">
-        <v>42.86</v>
+        <v>12</v>
       </c>
       <c r="I14" s="2">
-        <v>6.6</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J14">
         <v>0</v>
@@ -980,36 +958,263 @@
     </row>
     <row r="15" spans="1:11">
       <c r="A15" t="s">
+        <v>15</v>
+      </c>
+      <c r="D15">
+        <v>433</v>
+      </c>
+      <c r="E15">
+        <v>362</v>
+      </c>
+      <c r="F15">
+        <v>71</v>
+      </c>
+      <c r="G15" s="1">
+        <v>83.59999999999999</v>
+      </c>
+      <c r="H15" s="1">
+        <v>16.4</v>
+      </c>
+      <c r="I15" s="2">
+        <v>8</v>
+      </c>
+      <c r="J15">
+        <v>2</v>
+      </c>
+      <c r="K15" s="1">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11">
+      <c r="A16" t="s">
         <v>16</v>
       </c>
-      <c r="B15" t="s">
+      <c r="B16" t="s">
+        <v>18</v>
+      </c>
+      <c r="C16" t="s">
+        <v>29</v>
+      </c>
+      <c r="D16">
+        <v>41</v>
+      </c>
+      <c r="E16">
+        <v>41</v>
+      </c>
+      <c r="F16">
+        <v>0</v>
+      </c>
+      <c r="G16" s="1">
+        <v>100</v>
+      </c>
+      <c r="H16" s="1">
+        <v>0</v>
+      </c>
+      <c r="I16" s="2">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="J16">
+        <v>0</v>
+      </c>
+      <c r="K16" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11">
+      <c r="A17" t="s">
+        <v>16</v>
+      </c>
+      <c r="B17" t="s">
+        <v>18</v>
+      </c>
+      <c r="C17" t="s">
         <v>30</v>
       </c>
-      <c r="C15" t="s">
+      <c r="D17">
+        <v>27</v>
+      </c>
+      <c r="E17">
+        <v>25</v>
+      </c>
+      <c r="F17">
+        <v>2</v>
+      </c>
+      <c r="G17" s="1">
+        <v>92.59999999999999</v>
+      </c>
+      <c r="H17" s="1">
+        <v>7.4</v>
+      </c>
+      <c r="I17" s="2">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="J17">
+        <v>0</v>
+      </c>
+      <c r="K17" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11">
+      <c r="A18" t="s">
+        <v>16</v>
+      </c>
+      <c r="B18" t="s">
+        <v>18</v>
+      </c>
+      <c r="C18" t="s">
         <v>31</v>
       </c>
-      <c r="D15">
+      <c r="D18">
+        <v>41</v>
+      </c>
+      <c r="E18">
+        <v>39</v>
+      </c>
+      <c r="F18">
+        <v>2</v>
+      </c>
+      <c r="G18" s="1">
+        <v>95.09999999999999</v>
+      </c>
+      <c r="H18" s="1">
+        <v>4.9</v>
+      </c>
+      <c r="I18" s="2">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="J18">
+        <v>0</v>
+      </c>
+      <c r="K18" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11">
+      <c r="A19" t="s">
+        <v>16</v>
+      </c>
+      <c r="B19" t="s">
+        <v>18</v>
+      </c>
+      <c r="C19" t="s">
+        <v>32</v>
+      </c>
+      <c r="D19">
+        <v>14</v>
+      </c>
+      <c r="E19">
+        <v>8</v>
+      </c>
+      <c r="F19">
+        <v>6</v>
+      </c>
+      <c r="G19" s="1">
+        <v>57.1</v>
+      </c>
+      <c r="H19" s="1">
+        <v>42.9</v>
+      </c>
+      <c r="I19" s="2">
+        <v>6.6</v>
+      </c>
+      <c r="J19">
+        <v>0</v>
+      </c>
+      <c r="K19" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11">
+      <c r="A20" t="s">
+        <v>16</v>
+      </c>
+      <c r="D20">
+        <v>123</v>
+      </c>
+      <c r="E20">
+        <v>113</v>
+      </c>
+      <c r="F20">
+        <v>10</v>
+      </c>
+      <c r="G20" s="1">
+        <v>91.90000000000001</v>
+      </c>
+      <c r="H20" s="1">
+        <v>8.1</v>
+      </c>
+      <c r="I20" s="2">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="J20">
+        <v>0</v>
+      </c>
+      <c r="K20" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11">
+      <c r="A21" t="s">
+        <v>17</v>
+      </c>
+      <c r="B21" t="s">
+        <v>18</v>
+      </c>
+      <c r="C21" t="s">
+        <v>33</v>
+      </c>
+      <c r="D21">
         <v>25</v>
       </c>
-      <c r="E15">
+      <c r="E21">
         <v>9</v>
       </c>
-      <c r="F15">
+      <c r="F21">
         <v>16</v>
       </c>
-      <c r="G15" s="1">
+      <c r="G21" s="1">
         <v>36</v>
       </c>
-      <c r="H15" s="1">
+      <c r="H21" s="1">
         <v>64</v>
       </c>
-      <c r="I15" s="2">
+      <c r="I21" s="2">
         <v>5.7</v>
       </c>
-      <c r="J15">
-        <v>0</v>
-      </c>
-      <c r="K15" s="1">
+      <c r="J21">
+        <v>0</v>
+      </c>
+      <c r="K21" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11">
+      <c r="A22" t="s">
+        <v>17</v>
+      </c>
+      <c r="D22">
+        <v>25</v>
+      </c>
+      <c r="E22">
+        <v>9</v>
+      </c>
+      <c r="F22">
+        <v>16</v>
+      </c>
+      <c r="G22" s="1">
+        <v>36</v>
+      </c>
+      <c r="H22" s="1">
+        <v>64</v>
+      </c>
+      <c r="I22" s="2">
+        <v>5.7</v>
+      </c>
+      <c r="J22">
+        <v>0</v>
+      </c>
+      <c r="K22" s="1">
         <v>0</v>
       </c>
     </row>
@@ -1020,11 +1225,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K15"/>
+  <dimension ref="A1:K22"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
-    <col min="3" max="3" width="30.7109375" customWidth="1"/>
+    <col min="2" max="2" width="30.7109375" customWidth="1"/>
     <col min="7" max="8" width="9.140625" style="1"/>
     <col min="9" max="9" width="9.140625" style="2"/>
     <col min="11" max="11" width="9.140625" style="1"/>
@@ -1070,31 +1275,34 @@
         <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C2" t="s">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="D2">
         <v>38</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="F2">
-        <v>38</v>
+        <v>6</v>
       </c>
       <c r="G2" s="1">
-        <v>0</v>
+        <v>84.2</v>
       </c>
       <c r="H2" s="1">
-        <v>100</v>
+        <v>15.8</v>
+      </c>
+      <c r="I2" s="2">
+        <v>7.7</v>
       </c>
       <c r="J2">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="K2" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -1105,60 +1313,60 @@
         <v>18</v>
       </c>
       <c r="C3" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="D3">
         <v>32</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="F3">
-        <v>32</v>
+        <v>9</v>
       </c>
       <c r="G3" s="1">
-        <v>0</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="H3" s="1">
-        <v>100</v>
+        <v>28.1</v>
+      </c>
+      <c r="I3" s="2">
+        <v>6.5</v>
       </c>
       <c r="J3">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="K3" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:11">
       <c r="A4" t="s">
-        <v>12</v>
-      </c>
-      <c r="B4" t="s">
-        <v>19</v>
-      </c>
-      <c r="C4" t="s">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="D4">
-        <v>34</v>
+        <v>70</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="F4">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="G4" s="1">
-        <v>0</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="H4" s="1">
-        <v>100</v>
+        <v>21.4</v>
+      </c>
+      <c r="I4" s="2">
+        <v>7.1</v>
       </c>
       <c r="J4">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="K4" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -1166,159 +1374,162 @@
         <v>12</v>
       </c>
       <c r="B5" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C5" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="D5">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="F5">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="G5" s="1">
-        <v>0</v>
+        <v>76.5</v>
       </c>
       <c r="H5" s="1">
-        <v>100</v>
+        <v>23.5</v>
+      </c>
+      <c r="I5" s="2">
+        <v>7.1</v>
       </c>
       <c r="J5">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="K5" s="1">
-        <v>100</v>
+        <v>2.94</v>
       </c>
     </row>
     <row r="6" spans="1:11">
       <c r="A6" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B6" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C6" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="D6">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="F6">
-        <v>26</v>
+        <v>6</v>
       </c>
       <c r="G6" s="1">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="H6" s="1">
-        <v>100</v>
+        <v>20</v>
+      </c>
+      <c r="I6" s="2">
+        <v>7.1</v>
       </c>
       <c r="J6">
-        <v>26</v>
+        <v>1</v>
       </c>
       <c r="K6" s="1">
-        <v>100</v>
+        <v>3.33</v>
       </c>
     </row>
     <row r="7" spans="1:11">
       <c r="A7" t="s">
+        <v>12</v>
+      </c>
+      <c r="D7">
+        <v>64</v>
+      </c>
+      <c r="E7">
+        <v>50</v>
+      </c>
+      <c r="F7">
         <v>14</v>
       </c>
-      <c r="B7" t="s">
-        <v>22</v>
-      </c>
-      <c r="C7" t="s">
-        <v>31</v>
-      </c>
-      <c r="D7">
-        <v>31</v>
-      </c>
-      <c r="E7">
-        <v>0</v>
-      </c>
-      <c r="F7">
-        <v>31</v>
-      </c>
       <c r="G7" s="1">
-        <v>0</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="H7" s="1">
-        <v>100</v>
+        <v>21.9</v>
+      </c>
+      <c r="I7" s="2">
+        <v>7.1</v>
       </c>
       <c r="J7">
-        <v>31</v>
+        <v>2</v>
       </c>
       <c r="K7" s="1">
-        <v>100</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="8" spans="1:11">
       <c r="A8" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B8" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="C8" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="D8">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E8">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F8">
-        <v>28</v>
+        <v>1</v>
       </c>
       <c r="G8" s="1">
-        <v>0</v>
+        <v>96.2</v>
       </c>
       <c r="H8" s="1">
-        <v>100</v>
+        <v>3.8</v>
+      </c>
+      <c r="I8" s="2">
+        <v>9.1</v>
       </c>
       <c r="J8">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="K8" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:11">
       <c r="A9" t="s">
-        <v>14</v>
-      </c>
-      <c r="B9" t="s">
-        <v>24</v>
-      </c>
-      <c r="C9" t="s">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="D9">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="E9">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F9">
-        <v>34</v>
+        <v>1</v>
       </c>
       <c r="G9" s="1">
-        <v>0</v>
+        <v>96.2</v>
       </c>
       <c r="H9" s="1">
-        <v>100</v>
+        <v>3.8</v>
+      </c>
+      <c r="I9" s="2">
+        <v>9.1</v>
       </c>
       <c r="J9">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="K9" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -1326,732 +1537,429 @@
         <v>14</v>
       </c>
       <c r="B10" t="s">
+        <v>18</v>
+      </c>
+      <c r="C10" t="s">
         <v>25</v>
       </c>
-      <c r="C10" t="s">
-        <v>32</v>
-      </c>
       <c r="D10">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E10">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F10">
-        <v>32</v>
+        <v>6</v>
       </c>
       <c r="G10" s="1">
-        <v>0</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="H10" s="1">
-        <v>100</v>
+        <v>19.4</v>
+      </c>
+      <c r="I10" s="2">
+        <v>7.9</v>
       </c>
       <c r="J10">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="K10" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:11">
       <c r="A11" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B11" t="s">
+        <v>18</v>
+      </c>
+      <c r="C11" t="s">
         <v>26</v>
       </c>
-      <c r="C11" t="s">
-        <v>31</v>
-      </c>
       <c r="D11">
-        <v>41</v>
+        <v>28</v>
       </c>
       <c r="E11">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F11">
-        <v>41</v>
+        <v>8</v>
       </c>
       <c r="G11" s="1">
-        <v>0</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="H11" s="1">
-        <v>100</v>
+        <v>28.6</v>
+      </c>
+      <c r="I11" s="2">
+        <v>8.1</v>
       </c>
       <c r="J11">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="K11" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:11">
       <c r="A12" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B12" t="s">
+        <v>19</v>
+      </c>
+      <c r="C12" t="s">
         <v>27</v>
       </c>
-      <c r="C12" t="s">
-        <v>31</v>
-      </c>
       <c r="D12">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="E12">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="F12">
-        <v>27</v>
+        <v>1</v>
       </c>
       <c r="G12" s="1">
-        <v>0</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="H12" s="1">
-        <v>100</v>
+        <v>2.9</v>
+      </c>
+      <c r="I12" s="2">
+        <v>9</v>
       </c>
       <c r="J12">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="K12" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:11">
       <c r="A13" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C13" t="s">
         <v>28</v>
       </c>
-      <c r="C13" t="s">
-        <v>31</v>
-      </c>
       <c r="D13">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="E13">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="F13">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="G13" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H13" s="1">
-        <v>100</v>
+        <v>0</v>
+      </c>
+      <c r="I13" s="2">
+        <v>9.800000000000001</v>
       </c>
       <c r="J13">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="K13" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:11">
       <c r="A14" t="s">
+        <v>14</v>
+      </c>
+      <c r="D14">
+        <v>125</v>
+      </c>
+      <c r="E14">
+        <v>110</v>
+      </c>
+      <c r="F14">
         <v>15</v>
       </c>
-      <c r="B14" t="s">
-        <v>29</v>
-      </c>
-      <c r="C14" t="s">
-        <v>31</v>
-      </c>
-      <c r="D14">
-        <v>14</v>
-      </c>
-      <c r="E14">
-        <v>0</v>
-      </c>
-      <c r="F14">
-        <v>14</v>
-      </c>
       <c r="G14" s="1">
-        <v>0</v>
+        <v>88</v>
       </c>
       <c r="H14" s="1">
-        <v>100</v>
+        <v>12</v>
+      </c>
+      <c r="I14" s="2">
+        <v>8.699999999999999</v>
       </c>
       <c r="J14">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="K14" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:11">
       <c r="A15" t="s">
+        <v>15</v>
+      </c>
+      <c r="D15">
+        <v>433</v>
+      </c>
+      <c r="E15">
+        <v>362</v>
+      </c>
+      <c r="F15">
+        <v>71</v>
+      </c>
+      <c r="G15" s="1">
+        <v>83.59999999999999</v>
+      </c>
+      <c r="H15" s="1">
+        <v>16.4</v>
+      </c>
+      <c r="I15" s="2">
+        <v>8</v>
+      </c>
+      <c r="J15">
+        <v>2</v>
+      </c>
+      <c r="K15" s="1">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11">
+      <c r="A16" t="s">
         <v>16</v>
       </c>
-      <c r="B15" t="s">
+      <c r="B16" t="s">
+        <v>18</v>
+      </c>
+      <c r="C16" t="s">
+        <v>29</v>
+      </c>
+      <c r="D16">
+        <v>41</v>
+      </c>
+      <c r="E16">
+        <v>41</v>
+      </c>
+      <c r="F16">
+        <v>0</v>
+      </c>
+      <c r="G16" s="1">
+        <v>100</v>
+      </c>
+      <c r="H16" s="1">
+        <v>0</v>
+      </c>
+      <c r="I16" s="2">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="J16">
+        <v>0</v>
+      </c>
+      <c r="K16" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11">
+      <c r="A17" t="s">
+        <v>16</v>
+      </c>
+      <c r="B17" t="s">
+        <v>18</v>
+      </c>
+      <c r="C17" t="s">
         <v>30</v>
       </c>
-      <c r="C15" t="s">
+      <c r="D17">
+        <v>27</v>
+      </c>
+      <c r="E17">
+        <v>25</v>
+      </c>
+      <c r="F17">
+        <v>2</v>
+      </c>
+      <c r="G17" s="1">
+        <v>92.59999999999999</v>
+      </c>
+      <c r="H17" s="1">
+        <v>7.4</v>
+      </c>
+      <c r="I17" s="2">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="J17">
+        <v>0</v>
+      </c>
+      <c r="K17" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11">
+      <c r="A18" t="s">
+        <v>16</v>
+      </c>
+      <c r="B18" t="s">
+        <v>18</v>
+      </c>
+      <c r="C18" t="s">
         <v>31</v>
       </c>
-      <c r="D15">
+      <c r="D18">
+        <v>41</v>
+      </c>
+      <c r="E18">
+        <v>39</v>
+      </c>
+      <c r="F18">
+        <v>2</v>
+      </c>
+      <c r="G18" s="1">
+        <v>95.09999999999999</v>
+      </c>
+      <c r="H18" s="1">
+        <v>4.9</v>
+      </c>
+      <c r="I18" s="2">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="J18">
+        <v>0</v>
+      </c>
+      <c r="K18" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11">
+      <c r="A19" t="s">
+        <v>16</v>
+      </c>
+      <c r="B19" t="s">
+        <v>18</v>
+      </c>
+      <c r="C19" t="s">
+        <v>32</v>
+      </c>
+      <c r="D19">
+        <v>14</v>
+      </c>
+      <c r="E19">
+        <v>8</v>
+      </c>
+      <c r="F19">
+        <v>6</v>
+      </c>
+      <c r="G19" s="1">
+        <v>57.1</v>
+      </c>
+      <c r="H19" s="1">
+        <v>42.9</v>
+      </c>
+      <c r="I19" s="2">
+        <v>6.6</v>
+      </c>
+      <c r="J19">
+        <v>0</v>
+      </c>
+      <c r="K19" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11">
+      <c r="A20" t="s">
+        <v>16</v>
+      </c>
+      <c r="D20">
+        <v>123</v>
+      </c>
+      <c r="E20">
+        <v>113</v>
+      </c>
+      <c r="F20">
+        <v>10</v>
+      </c>
+      <c r="G20" s="1">
+        <v>91.90000000000001</v>
+      </c>
+      <c r="H20" s="1">
+        <v>8.1</v>
+      </c>
+      <c r="I20" s="2">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="J20">
+        <v>0</v>
+      </c>
+      <c r="K20" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11">
+      <c r="A21" t="s">
+        <v>17</v>
+      </c>
+      <c r="B21" t="s">
+        <v>18</v>
+      </c>
+      <c r="C21" t="s">
+        <v>33</v>
+      </c>
+      <c r="D21">
         <v>25</v>
       </c>
-      <c r="E15">
-        <v>0</v>
-      </c>
-      <c r="F15">
+      <c r="E21">
+        <v>9</v>
+      </c>
+      <c r="F21">
+        <v>16</v>
+      </c>
+      <c r="G21" s="1">
+        <v>36</v>
+      </c>
+      <c r="H21" s="1">
+        <v>64</v>
+      </c>
+      <c r="I21" s="2">
+        <v>6.1</v>
+      </c>
+      <c r="J21">
+        <v>0</v>
+      </c>
+      <c r="K21" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11">
+      <c r="A22" t="s">
+        <v>17</v>
+      </c>
+      <c r="D22">
         <v>25</v>
       </c>
-      <c r="G15" s="1">
-        <v>0</v>
-      </c>
-      <c r="H15" s="1">
-        <v>100</v>
-      </c>
-      <c r="J15">
-        <v>25</v>
-      </c>
-      <c r="K15" s="1">
-        <v>100</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K15"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="30.7109375" customWidth="1"/>
-    <col min="3" max="3" width="30.7109375" customWidth="1"/>
-    <col min="7" max="8" width="9.140625" style="1"/>
-    <col min="9" max="9" width="9.140625" style="2"/>
-    <col min="11" max="11" width="9.140625" style="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:11">
-      <c r="A1" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="3" t="s">
+      <c r="E22">
         <v>9</v>
       </c>
-      <c r="K1" s="3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11">
-      <c r="A2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C2" t="s">
-        <v>31</v>
-      </c>
-      <c r="D2">
-        <v>38</v>
-      </c>
-      <c r="E2">
-        <v>32</v>
-      </c>
-      <c r="F2">
-        <v>6</v>
-      </c>
-      <c r="G2" s="1">
-        <v>84.20999999999999</v>
-      </c>
-      <c r="H2" s="1">
-        <v>15.79</v>
-      </c>
-      <c r="I2" s="2">
-        <v>7.7</v>
-      </c>
-      <c r="J2">
-        <v>0</v>
-      </c>
-      <c r="K2" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11">
-      <c r="A3" t="s">
-        <v>11</v>
-      </c>
-      <c r="B3" t="s">
-        <v>18</v>
-      </c>
-      <c r="C3" t="s">
-        <v>31</v>
-      </c>
-      <c r="D3">
-        <v>32</v>
-      </c>
-      <c r="E3">
-        <v>23</v>
-      </c>
-      <c r="F3">
-        <v>9</v>
-      </c>
-      <c r="G3" s="1">
-        <v>71.88</v>
-      </c>
-      <c r="H3" s="1">
-        <v>28.13</v>
-      </c>
-      <c r="I3" s="2">
-        <v>6.5</v>
-      </c>
-      <c r="J3">
-        <v>0</v>
-      </c>
-      <c r="K3" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11">
-      <c r="A4" t="s">
-        <v>12</v>
-      </c>
-      <c r="B4" t="s">
-        <v>19</v>
-      </c>
-      <c r="C4" t="s">
-        <v>31</v>
-      </c>
-      <c r="D4">
-        <v>34</v>
-      </c>
-      <c r="E4">
-        <v>26</v>
-      </c>
-      <c r="F4">
-        <v>8</v>
-      </c>
-      <c r="G4" s="1">
-        <v>76.47</v>
-      </c>
-      <c r="H4" s="1">
-        <v>23.53</v>
-      </c>
-      <c r="I4" s="2">
-        <v>7.1</v>
-      </c>
-      <c r="J4">
-        <v>1</v>
-      </c>
-      <c r="K4" s="1">
-        <v>2.94</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11">
-      <c r="A5" t="s">
-        <v>12</v>
-      </c>
-      <c r="B5" t="s">
-        <v>20</v>
-      </c>
-      <c r="C5" t="s">
-        <v>31</v>
-      </c>
-      <c r="D5">
-        <v>30</v>
-      </c>
-      <c r="E5">
-        <v>24</v>
-      </c>
-      <c r="F5">
-        <v>6</v>
-      </c>
-      <c r="G5" s="1">
-        <v>80</v>
-      </c>
-      <c r="H5" s="1">
-        <v>20</v>
-      </c>
-      <c r="I5" s="2">
-        <v>7.1</v>
-      </c>
-      <c r="J5">
-        <v>1</v>
-      </c>
-      <c r="K5" s="1">
-        <v>3.33</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11">
-      <c r="A6" t="s">
-        <v>13</v>
-      </c>
-      <c r="B6" t="s">
-        <v>21</v>
-      </c>
-      <c r="C6" t="s">
-        <v>32</v>
-      </c>
-      <c r="D6">
-        <v>26</v>
-      </c>
-      <c r="E6">
-        <v>25</v>
-      </c>
-      <c r="F6">
-        <v>1</v>
-      </c>
-      <c r="G6" s="1">
-        <v>96.15000000000001</v>
-      </c>
-      <c r="H6" s="1">
-        <v>3.85</v>
-      </c>
-      <c r="I6" s="2">
-        <v>9.1</v>
-      </c>
-      <c r="J6">
-        <v>0</v>
-      </c>
-      <c r="K6" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11">
-      <c r="A7" t="s">
-        <v>14</v>
-      </c>
-      <c r="B7" t="s">
-        <v>22</v>
-      </c>
-      <c r="C7" t="s">
-        <v>31</v>
-      </c>
-      <c r="D7">
-        <v>31</v>
-      </c>
-      <c r="E7">
-        <v>25</v>
-      </c>
-      <c r="F7">
-        <v>6</v>
-      </c>
-      <c r="G7" s="1">
-        <v>80.65000000000001</v>
-      </c>
-      <c r="H7" s="1">
-        <v>19.35</v>
-      </c>
-      <c r="I7" s="2">
-        <v>7.9</v>
-      </c>
-      <c r="J7">
-        <v>0</v>
-      </c>
-      <c r="K7" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11">
-      <c r="A8" t="s">
-        <v>14</v>
-      </c>
-      <c r="B8" t="s">
-        <v>23</v>
-      </c>
-      <c r="C8" t="s">
-        <v>31</v>
-      </c>
-      <c r="D8">
-        <v>28</v>
-      </c>
-      <c r="E8">
-        <v>20</v>
-      </c>
-      <c r="F8">
-        <v>8</v>
-      </c>
-      <c r="G8" s="1">
-        <v>71.43000000000001</v>
-      </c>
-      <c r="H8" s="1">
-        <v>28.57</v>
-      </c>
-      <c r="I8" s="2">
-        <v>8.1</v>
-      </c>
-      <c r="J8">
-        <v>0</v>
-      </c>
-      <c r="K8" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11">
-      <c r="A9" t="s">
-        <v>14</v>
-      </c>
-      <c r="B9" t="s">
-        <v>24</v>
-      </c>
-      <c r="C9" t="s">
-        <v>32</v>
-      </c>
-      <c r="D9">
-        <v>34</v>
-      </c>
-      <c r="E9">
-        <v>33</v>
-      </c>
-      <c r="F9">
-        <v>1</v>
-      </c>
-      <c r="G9" s="1">
-        <v>97.06</v>
-      </c>
-      <c r="H9" s="1">
-        <v>2.94</v>
-      </c>
-      <c r="I9" s="2">
-        <v>9</v>
-      </c>
-      <c r="J9">
-        <v>0</v>
-      </c>
-      <c r="K9" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11">
-      <c r="A10" t="s">
-        <v>14</v>
-      </c>
-      <c r="B10" t="s">
-        <v>25</v>
-      </c>
-      <c r="C10" t="s">
-        <v>32</v>
-      </c>
-      <c r="D10">
-        <v>32</v>
-      </c>
-      <c r="E10">
-        <v>32</v>
-      </c>
-      <c r="F10">
-        <v>0</v>
-      </c>
-      <c r="G10" s="1">
-        <v>100</v>
-      </c>
-      <c r="H10" s="1">
-        <v>0</v>
-      </c>
-      <c r="I10" s="2">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="J10">
-        <v>0</v>
-      </c>
-      <c r="K10" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11">
-      <c r="A11" t="s">
-        <v>15</v>
-      </c>
-      <c r="B11" t="s">
-        <v>26</v>
-      </c>
-      <c r="C11" t="s">
-        <v>31</v>
-      </c>
-      <c r="D11">
-        <v>41</v>
-      </c>
-      <c r="E11">
-        <v>41</v>
-      </c>
-      <c r="F11">
-        <v>0</v>
-      </c>
-      <c r="G11" s="1">
-        <v>100</v>
-      </c>
-      <c r="H11" s="1">
-        <v>0</v>
-      </c>
-      <c r="I11" s="2">
-        <v>9.300000000000001</v>
-      </c>
-      <c r="J11">
-        <v>0</v>
-      </c>
-      <c r="K11" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11">
-      <c r="A12" t="s">
-        <v>15</v>
-      </c>
-      <c r="B12" t="s">
-        <v>27</v>
-      </c>
-      <c r="C12" t="s">
-        <v>31</v>
-      </c>
-      <c r="D12">
-        <v>27</v>
-      </c>
-      <c r="E12">
-        <v>25</v>
-      </c>
-      <c r="F12">
-        <v>2</v>
-      </c>
-      <c r="G12" s="1">
-        <v>92.59</v>
-      </c>
-      <c r="H12" s="1">
-        <v>7.41</v>
-      </c>
-      <c r="I12" s="2">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="J12">
-        <v>0</v>
-      </c>
-      <c r="K12" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11">
-      <c r="A13" t="s">
-        <v>15</v>
-      </c>
-      <c r="B13" t="s">
-        <v>28</v>
-      </c>
-      <c r="C13" t="s">
-        <v>31</v>
-      </c>
-      <c r="D13">
-        <v>41</v>
-      </c>
-      <c r="E13">
-        <v>39</v>
-      </c>
-      <c r="F13">
-        <v>2</v>
-      </c>
-      <c r="G13" s="1">
-        <v>95.12</v>
-      </c>
-      <c r="H13" s="1">
-        <v>4.88</v>
-      </c>
-      <c r="I13" s="2">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="J13">
-        <v>0</v>
-      </c>
-      <c r="K13" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11">
-      <c r="A14" t="s">
-        <v>15</v>
-      </c>
-      <c r="B14" t="s">
-        <v>29</v>
-      </c>
-      <c r="C14" t="s">
-        <v>31</v>
-      </c>
-      <c r="D14">
-        <v>14</v>
-      </c>
-      <c r="E14">
-        <v>8</v>
-      </c>
-      <c r="F14">
-        <v>6</v>
-      </c>
-      <c r="G14" s="1">
-        <v>57.14</v>
-      </c>
-      <c r="H14" s="1">
-        <v>42.86</v>
-      </c>
-      <c r="I14" s="2">
-        <v>6.6</v>
-      </c>
-      <c r="J14">
-        <v>0</v>
-      </c>
-      <c r="K14" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11">
-      <c r="A15" t="s">
+      <c r="F22">
         <v>16</v>
       </c>
-      <c r="B15" t="s">
-        <v>30</v>
-      </c>
-      <c r="C15" t="s">
-        <v>31</v>
-      </c>
-      <c r="D15">
-        <v>25</v>
-      </c>
-      <c r="E15">
-        <v>9</v>
-      </c>
-      <c r="F15">
-        <v>16</v>
-      </c>
-      <c r="G15" s="1">
+      <c r="G22" s="1">
         <v>36</v>
       </c>
-      <c r="H15" s="1">
+      <c r="H22" s="1">
         <v>64</v>
       </c>
-      <c r="I15" s="2">
+      <c r="I22" s="2">
         <v>6.1</v>
       </c>
-      <c r="J15">
-        <v>0</v>
-      </c>
-      <c r="K15" s="1">
+      <c r="J22">
+        <v>0</v>
+      </c>
+      <c r="K22" s="1">
         <v>0</v>
       </c>
     </row>

--- a/academias/Biología - Estadisticos 20222.xlsx
+++ b/academias/Biología - Estadisticos 20222.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="35">
   <si>
     <t>Docente</t>
   </si>
@@ -62,9 +62,6 @@
     <t>Rivera Cruz Ezequiel</t>
   </si>
   <si>
-    <t>Total</t>
-  </si>
-  <si>
     <t>Vargas Olvera Francisco Eduardo</t>
   </si>
   <si>
@@ -74,7 +71,13 @@
     <t>ECOLOGÍA</t>
   </si>
   <si>
+    <t>Totales Docente</t>
+  </si>
+  <si>
     <t>TEMAS DE BIOLOGÍA CONTEMPORÁNEA</t>
+  </si>
+  <si>
+    <t>Totales Generales</t>
   </si>
   <si>
     <t>4ARHM</t>
@@ -484,7 +487,7 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
-    <col min="2" max="2" width="30.7109375" customWidth="1"/>
+    <col min="2" max="2" width="50.7109375" customWidth="1"/>
     <col min="7" max="8" width="9.140625" style="1"/>
     <col min="9" max="9" width="9.140625" style="2"/>
     <col min="11" max="11" width="9.140625" style="1"/>
@@ -530,10 +533,10 @@
         <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D2">
         <v>38</v>
@@ -565,10 +568,10 @@
         <v>11</v>
       </c>
       <c r="B3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D3">
         <v>32</v>
@@ -599,6 +602,9 @@
       <c r="A4" t="s">
         <v>11</v>
       </c>
+      <c r="B4" t="s">
+        <v>18</v>
+      </c>
       <c r="D4">
         <v>70</v>
       </c>
@@ -629,10 +635,10 @@
         <v>12</v>
       </c>
       <c r="B5" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C5" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D5">
         <v>34</v>
@@ -664,10 +670,10 @@
         <v>12</v>
       </c>
       <c r="B6" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D6">
         <v>30</v>
@@ -698,6 +704,9 @@
       <c r="A7" t="s">
         <v>12</v>
       </c>
+      <c r="B7" t="s">
+        <v>18</v>
+      </c>
       <c r="D7">
         <v>64</v>
       </c>
@@ -731,7 +740,7 @@
         <v>19</v>
       </c>
       <c r="C8" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D8">
         <v>26</v>
@@ -762,6 +771,9 @@
       <c r="A9" t="s">
         <v>13</v>
       </c>
+      <c r="B9" t="s">
+        <v>18</v>
+      </c>
       <c r="D9">
         <v>26</v>
       </c>
@@ -792,10 +804,10 @@
         <v>14</v>
       </c>
       <c r="B10" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C10" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D10">
         <v>31</v>
@@ -827,10 +839,10 @@
         <v>14</v>
       </c>
       <c r="B11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C11" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D11">
         <v>28</v>
@@ -865,7 +877,7 @@
         <v>19</v>
       </c>
       <c r="C12" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D12">
         <v>34</v>
@@ -900,7 +912,7 @@
         <v>19</v>
       </c>
       <c r="C13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D13">
         <v>32</v>
@@ -931,6 +943,9 @@
       <c r="A14" t="s">
         <v>14</v>
       </c>
+      <c r="B14" t="s">
+        <v>18</v>
+      </c>
       <c r="D14">
         <v>125</v>
       </c>
@@ -960,58 +975,64 @@
       <c r="A15" t="s">
         <v>15</v>
       </c>
+      <c r="B15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C15" t="s">
+        <v>30</v>
+      </c>
       <c r="D15">
-        <v>433</v>
+        <v>41</v>
       </c>
       <c r="E15">
-        <v>362</v>
+        <v>41</v>
       </c>
       <c r="F15">
-        <v>71</v>
+        <v>0</v>
       </c>
       <c r="G15" s="1">
-        <v>83.59999999999999</v>
+        <v>100</v>
       </c>
       <c r="H15" s="1">
-        <v>16.4</v>
+        <v>0</v>
       </c>
       <c r="I15" s="2">
-        <v>8</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J15">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K15" s="1">
-        <v>0.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:11">
       <c r="A16" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C16" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D16">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="E16">
-        <v>41</v>
+        <v>25</v>
       </c>
       <c r="F16">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G16" s="1">
-        <v>100</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="H16" s="1">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="I16" s="2">
-        <v>9.300000000000001</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J16">
         <v>0</v>
@@ -1022,28 +1043,28 @@
     </row>
     <row r="17" spans="1:11">
       <c r="A17" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C17" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D17">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="E17">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="F17">
         <v>2</v>
       </c>
       <c r="G17" s="1">
-        <v>92.59999999999999</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="H17" s="1">
-        <v>7.4</v>
+        <v>4.9</v>
       </c>
       <c r="I17" s="2">
         <v>8.699999999999999</v>
@@ -1057,31 +1078,31 @@
     </row>
     <row r="18" spans="1:11">
       <c r="A18" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B18" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C18" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D18">
-        <v>41</v>
+        <v>14</v>
       </c>
       <c r="E18">
-        <v>39</v>
+        <v>8</v>
       </c>
       <c r="F18">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G18" s="1">
-        <v>95.09999999999999</v>
+        <v>57.1</v>
       </c>
       <c r="H18" s="1">
-        <v>4.9</v>
+        <v>42.9</v>
       </c>
       <c r="I18" s="2">
-        <v>8.699999999999999</v>
+        <v>6.6</v>
       </c>
       <c r="J18">
         <v>0</v>
@@ -1092,31 +1113,28 @@
     </row>
     <row r="19" spans="1:11">
       <c r="A19" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B19" t="s">
         <v>18</v>
       </c>
-      <c r="C19" t="s">
-        <v>32</v>
-      </c>
       <c r="D19">
-        <v>14</v>
+        <v>123</v>
       </c>
       <c r="E19">
-        <v>8</v>
+        <v>113</v>
       </c>
       <c r="F19">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G19" s="1">
-        <v>57.1</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="H19" s="1">
-        <v>42.9</v>
+        <v>8.1</v>
       </c>
       <c r="I19" s="2">
-        <v>6.6</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J19">
         <v>0</v>
@@ -1129,23 +1147,29 @@
       <c r="A20" t="s">
         <v>16</v>
       </c>
+      <c r="B20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C20" t="s">
+        <v>34</v>
+      </c>
       <c r="D20">
-        <v>123</v>
+        <v>25</v>
       </c>
       <c r="E20">
-        <v>113</v>
+        <v>9</v>
       </c>
       <c r="F20">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="G20" s="1">
-        <v>91.90000000000001</v>
+        <v>36</v>
       </c>
       <c r="H20" s="1">
-        <v>8.1</v>
+        <v>64</v>
       </c>
       <c r="I20" s="2">
-        <v>8.300000000000001</v>
+        <v>5.7</v>
       </c>
       <c r="J20">
         <v>0</v>
@@ -1156,14 +1180,11 @@
     </row>
     <row r="21" spans="1:11">
       <c r="A21" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B21" t="s">
         <v>18</v>
       </c>
-      <c r="C21" t="s">
-        <v>33</v>
-      </c>
       <c r="D21">
         <v>25</v>
       </c>
@@ -1190,32 +1211,32 @@
       </c>
     </row>
     <row r="22" spans="1:11">
-      <c r="A22" t="s">
-        <v>17</v>
+      <c r="B22" t="s">
+        <v>20</v>
       </c>
       <c r="D22">
-        <v>25</v>
+        <v>433</v>
       </c>
       <c r="E22">
-        <v>9</v>
+        <v>362</v>
       </c>
       <c r="F22">
-        <v>16</v>
+        <v>71</v>
       </c>
       <c r="G22" s="1">
-        <v>36</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="H22" s="1">
-        <v>64</v>
+        <v>16.4</v>
       </c>
       <c r="I22" s="2">
-        <v>5.7</v>
+        <v>8</v>
       </c>
       <c r="J22">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K22" s="1">
-        <v>0</v>
+        <v>0.5</v>
       </c>
     </row>
   </sheetData>
@@ -1275,10 +1296,10 @@
         <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D2">
         <v>38</v>
@@ -1310,10 +1331,10 @@
         <v>11</v>
       </c>
       <c r="B3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D3">
         <v>32</v>
@@ -1344,6 +1365,9 @@
       <c r="A4" t="s">
         <v>11</v>
       </c>
+      <c r="B4" t="s">
+        <v>18</v>
+      </c>
       <c r="D4">
         <v>70</v>
       </c>
@@ -1374,10 +1398,10 @@
         <v>12</v>
       </c>
       <c r="B5" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C5" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D5">
         <v>34</v>
@@ -1409,10 +1433,10 @@
         <v>12</v>
       </c>
       <c r="B6" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D6">
         <v>30</v>
@@ -1443,6 +1467,9 @@
       <c r="A7" t="s">
         <v>12</v>
       </c>
+      <c r="B7" t="s">
+        <v>18</v>
+      </c>
       <c r="D7">
         <v>64</v>
       </c>
@@ -1476,7 +1503,7 @@
         <v>19</v>
       </c>
       <c r="C8" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D8">
         <v>26</v>
@@ -1507,6 +1534,9 @@
       <c r="A9" t="s">
         <v>13</v>
       </c>
+      <c r="B9" t="s">
+        <v>18</v>
+      </c>
       <c r="D9">
         <v>26</v>
       </c>
@@ -1537,10 +1567,10 @@
         <v>14</v>
       </c>
       <c r="B10" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C10" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D10">
         <v>31</v>
@@ -1572,10 +1602,10 @@
         <v>14</v>
       </c>
       <c r="B11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C11" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D11">
         <v>28</v>
@@ -1610,7 +1640,7 @@
         <v>19</v>
       </c>
       <c r="C12" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D12">
         <v>34</v>
@@ -1645,7 +1675,7 @@
         <v>19</v>
       </c>
       <c r="C13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D13">
         <v>32</v>
@@ -1676,6 +1706,9 @@
       <c r="A14" t="s">
         <v>14</v>
       </c>
+      <c r="B14" t="s">
+        <v>18</v>
+      </c>
       <c r="D14">
         <v>125</v>
       </c>
@@ -1705,58 +1738,64 @@
       <c r="A15" t="s">
         <v>15</v>
       </c>
+      <c r="B15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C15" t="s">
+        <v>30</v>
+      </c>
       <c r="D15">
-        <v>433</v>
+        <v>41</v>
       </c>
       <c r="E15">
-        <v>362</v>
+        <v>41</v>
       </c>
       <c r="F15">
-        <v>71</v>
+        <v>0</v>
       </c>
       <c r="G15" s="1">
-        <v>83.59999999999999</v>
+        <v>100</v>
       </c>
       <c r="H15" s="1">
-        <v>16.4</v>
+        <v>0</v>
       </c>
       <c r="I15" s="2">
-        <v>8</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J15">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K15" s="1">
-        <v>0.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:11">
       <c r="A16" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C16" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D16">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="E16">
-        <v>41</v>
+        <v>25</v>
       </c>
       <c r="F16">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G16" s="1">
-        <v>100</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="H16" s="1">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="I16" s="2">
-        <v>9.300000000000001</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J16">
         <v>0</v>
@@ -1767,28 +1806,28 @@
     </row>
     <row r="17" spans="1:11">
       <c r="A17" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C17" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D17">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="E17">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="F17">
         <v>2</v>
       </c>
       <c r="G17" s="1">
-        <v>92.59999999999999</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="H17" s="1">
-        <v>7.4</v>
+        <v>4.9</v>
       </c>
       <c r="I17" s="2">
         <v>8.699999999999999</v>
@@ -1802,31 +1841,31 @@
     </row>
     <row r="18" spans="1:11">
       <c r="A18" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B18" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C18" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D18">
-        <v>41</v>
+        <v>14</v>
       </c>
       <c r="E18">
-        <v>39</v>
+        <v>8</v>
       </c>
       <c r="F18">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G18" s="1">
-        <v>95.09999999999999</v>
+        <v>57.1</v>
       </c>
       <c r="H18" s="1">
-        <v>4.9</v>
+        <v>42.9</v>
       </c>
       <c r="I18" s="2">
-        <v>8.699999999999999</v>
+        <v>6.6</v>
       </c>
       <c r="J18">
         <v>0</v>
@@ -1837,31 +1876,28 @@
     </row>
     <row r="19" spans="1:11">
       <c r="A19" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B19" t="s">
         <v>18</v>
       </c>
-      <c r="C19" t="s">
-        <v>32</v>
-      </c>
       <c r="D19">
-        <v>14</v>
+        <v>123</v>
       </c>
       <c r="E19">
-        <v>8</v>
+        <v>113</v>
       </c>
       <c r="F19">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G19" s="1">
-        <v>57.1</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="H19" s="1">
-        <v>42.9</v>
+        <v>8.1</v>
       </c>
       <c r="I19" s="2">
-        <v>6.6</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J19">
         <v>0</v>
@@ -1874,23 +1910,29 @@
       <c r="A20" t="s">
         <v>16</v>
       </c>
+      <c r="B20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C20" t="s">
+        <v>34</v>
+      </c>
       <c r="D20">
-        <v>123</v>
+        <v>25</v>
       </c>
       <c r="E20">
-        <v>113</v>
+        <v>9</v>
       </c>
       <c r="F20">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="G20" s="1">
-        <v>91.90000000000001</v>
+        <v>36</v>
       </c>
       <c r="H20" s="1">
-        <v>8.1</v>
+        <v>64</v>
       </c>
       <c r="I20" s="2">
-        <v>8.300000000000001</v>
+        <v>6.1</v>
       </c>
       <c r="J20">
         <v>0</v>
@@ -1901,14 +1943,11 @@
     </row>
     <row r="21" spans="1:11">
       <c r="A21" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B21" t="s">
         <v>18</v>
       </c>
-      <c r="C21" t="s">
-        <v>33</v>
-      </c>
       <c r="D21">
         <v>25</v>
       </c>
@@ -1935,32 +1974,32 @@
       </c>
     </row>
     <row r="22" spans="1:11">
-      <c r="A22" t="s">
-        <v>17</v>
+      <c r="B22" t="s">
+        <v>20</v>
       </c>
       <c r="D22">
-        <v>25</v>
+        <v>433</v>
       </c>
       <c r="E22">
-        <v>9</v>
+        <v>362</v>
       </c>
       <c r="F22">
-        <v>16</v>
+        <v>71</v>
       </c>
       <c r="G22" s="1">
-        <v>36</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="H22" s="1">
-        <v>64</v>
+        <v>16.4</v>
       </c>
       <c r="I22" s="2">
-        <v>6.1</v>
+        <v>8</v>
       </c>
       <c r="J22">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K22" s="1">
-        <v>0</v>
+        <v>0.5</v>
       </c>
     </row>
   </sheetData>

--- a/academias/Biología - Estadisticos 20222.xlsx
+++ b/academias/Biología - Estadisticos 20222.xlsx
@@ -8,14 +8,15 @@
   </bookViews>
   <sheets>
     <sheet name="1er Parcial" sheetId="1" r:id="rId1"/>
-    <sheet name="Final" sheetId="2" r:id="rId2"/>
+    <sheet name="2o Parcial" sheetId="2" r:id="rId2"/>
+    <sheet name="Final" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="35">
   <si>
     <t>Docente</t>
   </si>
@@ -1305,6 +1306,769 @@
         <v>38</v>
       </c>
       <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2">
+        <v>38</v>
+      </c>
+      <c r="G2" s="1">
+        <v>0</v>
+      </c>
+      <c r="H2" s="1">
+        <v>100</v>
+      </c>
+      <c r="I2" s="2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>38</v>
+      </c>
+      <c r="K2" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11">
+      <c r="A3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D3">
+        <v>32</v>
+      </c>
+      <c r="E3">
+        <v>0</v>
+      </c>
+      <c r="F3">
+        <v>32</v>
+      </c>
+      <c r="G3" s="1">
+        <v>0</v>
+      </c>
+      <c r="H3" s="1">
+        <v>100</v>
+      </c>
+      <c r="I3" s="2">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>32</v>
+      </c>
+      <c r="K3" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11">
+      <c r="A4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" t="s">
+        <v>18</v>
+      </c>
+      <c r="D4">
+        <v>70</v>
+      </c>
+      <c r="E4">
+        <v>0</v>
+      </c>
+      <c r="F4">
+        <v>70</v>
+      </c>
+      <c r="G4" s="1">
+        <v>0</v>
+      </c>
+      <c r="H4" s="1">
+        <v>100</v>
+      </c>
+      <c r="I4" s="2">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>70</v>
+      </c>
+      <c r="K4" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11">
+      <c r="A5" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5" t="s">
+        <v>23</v>
+      </c>
+      <c r="D5">
+        <v>34</v>
+      </c>
+      <c r="E5">
+        <v>0</v>
+      </c>
+      <c r="F5">
+        <v>34</v>
+      </c>
+      <c r="G5" s="1">
+        <v>0</v>
+      </c>
+      <c r="H5" s="1">
+        <v>100</v>
+      </c>
+      <c r="I5" s="2">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>34</v>
+      </c>
+      <c r="K5" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11">
+      <c r="A6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D6">
+        <v>30</v>
+      </c>
+      <c r="E6">
+        <v>0</v>
+      </c>
+      <c r="F6">
+        <v>30</v>
+      </c>
+      <c r="G6" s="1">
+        <v>0</v>
+      </c>
+      <c r="H6" s="1">
+        <v>100</v>
+      </c>
+      <c r="I6" s="2">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>30</v>
+      </c>
+      <c r="K6" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11">
+      <c r="A7" t="s">
+        <v>12</v>
+      </c>
+      <c r="B7" t="s">
+        <v>18</v>
+      </c>
+      <c r="D7">
+        <v>64</v>
+      </c>
+      <c r="E7">
+        <v>0</v>
+      </c>
+      <c r="F7">
+        <v>64</v>
+      </c>
+      <c r="G7" s="1">
+        <v>0</v>
+      </c>
+      <c r="H7" s="1">
+        <v>100</v>
+      </c>
+      <c r="I7" s="2">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>64</v>
+      </c>
+      <c r="K7" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11">
+      <c r="A8" t="s">
+        <v>13</v>
+      </c>
+      <c r="B8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" t="s">
+        <v>25</v>
+      </c>
+      <c r="D8">
+        <v>26</v>
+      </c>
+      <c r="E8">
+        <v>0</v>
+      </c>
+      <c r="F8">
+        <v>26</v>
+      </c>
+      <c r="G8" s="1">
+        <v>0</v>
+      </c>
+      <c r="H8" s="1">
+        <v>100</v>
+      </c>
+      <c r="I8" s="2">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>26</v>
+      </c>
+      <c r="K8" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11">
+      <c r="A9" t="s">
+        <v>13</v>
+      </c>
+      <c r="B9" t="s">
+        <v>18</v>
+      </c>
+      <c r="D9">
+        <v>26</v>
+      </c>
+      <c r="E9">
+        <v>0</v>
+      </c>
+      <c r="F9">
+        <v>26</v>
+      </c>
+      <c r="G9" s="1">
+        <v>0</v>
+      </c>
+      <c r="H9" s="1">
+        <v>100</v>
+      </c>
+      <c r="I9" s="2">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>26</v>
+      </c>
+      <c r="K9" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11">
+      <c r="A10" t="s">
+        <v>14</v>
+      </c>
+      <c r="B10" t="s">
+        <v>17</v>
+      </c>
+      <c r="C10" t="s">
+        <v>26</v>
+      </c>
+      <c r="D10">
+        <v>31</v>
+      </c>
+      <c r="E10">
+        <v>0</v>
+      </c>
+      <c r="F10">
+        <v>31</v>
+      </c>
+      <c r="G10" s="1">
+        <v>0</v>
+      </c>
+      <c r="H10" s="1">
+        <v>100</v>
+      </c>
+      <c r="I10" s="2">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>31</v>
+      </c>
+      <c r="K10" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11">
+      <c r="A11" t="s">
+        <v>14</v>
+      </c>
+      <c r="B11" t="s">
+        <v>17</v>
+      </c>
+      <c r="C11" t="s">
+        <v>27</v>
+      </c>
+      <c r="D11">
+        <v>28</v>
+      </c>
+      <c r="E11">
+        <v>0</v>
+      </c>
+      <c r="F11">
+        <v>28</v>
+      </c>
+      <c r="G11" s="1">
+        <v>0</v>
+      </c>
+      <c r="H11" s="1">
+        <v>100</v>
+      </c>
+      <c r="I11" s="2">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>28</v>
+      </c>
+      <c r="K11" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11">
+      <c r="A12" t="s">
+        <v>14</v>
+      </c>
+      <c r="B12" t="s">
+        <v>19</v>
+      </c>
+      <c r="C12" t="s">
+        <v>28</v>
+      </c>
+      <c r="D12">
+        <v>34</v>
+      </c>
+      <c r="E12">
+        <v>0</v>
+      </c>
+      <c r="F12">
+        <v>34</v>
+      </c>
+      <c r="G12" s="1">
+        <v>0</v>
+      </c>
+      <c r="H12" s="1">
+        <v>100</v>
+      </c>
+      <c r="I12" s="2">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>34</v>
+      </c>
+      <c r="K12" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11">
+      <c r="A13" t="s">
+        <v>14</v>
+      </c>
+      <c r="B13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C13" t="s">
+        <v>29</v>
+      </c>
+      <c r="D13">
+        <v>32</v>
+      </c>
+      <c r="E13">
+        <v>0</v>
+      </c>
+      <c r="F13">
+        <v>32</v>
+      </c>
+      <c r="G13" s="1">
+        <v>0</v>
+      </c>
+      <c r="H13" s="1">
+        <v>100</v>
+      </c>
+      <c r="I13" s="2">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>32</v>
+      </c>
+      <c r="K13" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11">
+      <c r="A14" t="s">
+        <v>14</v>
+      </c>
+      <c r="B14" t="s">
+        <v>18</v>
+      </c>
+      <c r="D14">
+        <v>125</v>
+      </c>
+      <c r="E14">
+        <v>0</v>
+      </c>
+      <c r="F14">
+        <v>125</v>
+      </c>
+      <c r="G14" s="1">
+        <v>0</v>
+      </c>
+      <c r="H14" s="1">
+        <v>100</v>
+      </c>
+      <c r="I14" s="2">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>125</v>
+      </c>
+      <c r="K14" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11">
+      <c r="A15" t="s">
+        <v>15</v>
+      </c>
+      <c r="B15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C15" t="s">
+        <v>30</v>
+      </c>
+      <c r="D15">
+        <v>41</v>
+      </c>
+      <c r="E15">
+        <v>0</v>
+      </c>
+      <c r="F15">
+        <v>41</v>
+      </c>
+      <c r="G15" s="1">
+        <v>0</v>
+      </c>
+      <c r="H15" s="1">
+        <v>100</v>
+      </c>
+      <c r="I15" s="2">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>41</v>
+      </c>
+      <c r="K15" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11">
+      <c r="A16" t="s">
+        <v>15</v>
+      </c>
+      <c r="B16" t="s">
+        <v>17</v>
+      </c>
+      <c r="C16" t="s">
+        <v>31</v>
+      </c>
+      <c r="D16">
+        <v>27</v>
+      </c>
+      <c r="E16">
+        <v>0</v>
+      </c>
+      <c r="F16">
+        <v>27</v>
+      </c>
+      <c r="G16" s="1">
+        <v>0</v>
+      </c>
+      <c r="H16" s="1">
+        <v>100</v>
+      </c>
+      <c r="I16" s="2">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>27</v>
+      </c>
+      <c r="K16" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11">
+      <c r="A17" t="s">
+        <v>15</v>
+      </c>
+      <c r="B17" t="s">
+        <v>17</v>
+      </c>
+      <c r="C17" t="s">
+        <v>32</v>
+      </c>
+      <c r="D17">
+        <v>41</v>
+      </c>
+      <c r="E17">
+        <v>0</v>
+      </c>
+      <c r="F17">
+        <v>41</v>
+      </c>
+      <c r="G17" s="1">
+        <v>0</v>
+      </c>
+      <c r="H17" s="1">
+        <v>100</v>
+      </c>
+      <c r="I17" s="2">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>41</v>
+      </c>
+      <c r="K17" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11">
+      <c r="A18" t="s">
+        <v>15</v>
+      </c>
+      <c r="B18" t="s">
+        <v>17</v>
+      </c>
+      <c r="C18" t="s">
+        <v>33</v>
+      </c>
+      <c r="D18">
+        <v>14</v>
+      </c>
+      <c r="E18">
+        <v>0</v>
+      </c>
+      <c r="F18">
+        <v>14</v>
+      </c>
+      <c r="G18" s="1">
+        <v>0</v>
+      </c>
+      <c r="H18" s="1">
+        <v>100</v>
+      </c>
+      <c r="I18" s="2">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>14</v>
+      </c>
+      <c r="K18" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11">
+      <c r="A19" t="s">
+        <v>15</v>
+      </c>
+      <c r="B19" t="s">
+        <v>18</v>
+      </c>
+      <c r="D19">
+        <v>123</v>
+      </c>
+      <c r="E19">
+        <v>0</v>
+      </c>
+      <c r="F19">
+        <v>123</v>
+      </c>
+      <c r="G19" s="1">
+        <v>0</v>
+      </c>
+      <c r="H19" s="1">
+        <v>100</v>
+      </c>
+      <c r="I19" s="2">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>123</v>
+      </c>
+      <c r="K19" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11">
+      <c r="A20" t="s">
+        <v>16</v>
+      </c>
+      <c r="B20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C20" t="s">
+        <v>34</v>
+      </c>
+      <c r="D20">
+        <v>25</v>
+      </c>
+      <c r="E20">
+        <v>0</v>
+      </c>
+      <c r="F20">
+        <v>25</v>
+      </c>
+      <c r="G20" s="1">
+        <v>0</v>
+      </c>
+      <c r="H20" s="1">
+        <v>100</v>
+      </c>
+      <c r="I20" s="2">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>25</v>
+      </c>
+      <c r="K20" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11">
+      <c r="A21" t="s">
+        <v>16</v>
+      </c>
+      <c r="B21" t="s">
+        <v>18</v>
+      </c>
+      <c r="D21">
+        <v>25</v>
+      </c>
+      <c r="E21">
+        <v>0</v>
+      </c>
+      <c r="F21">
+        <v>25</v>
+      </c>
+      <c r="G21" s="1">
+        <v>0</v>
+      </c>
+      <c r="H21" s="1">
+        <v>100</v>
+      </c>
+      <c r="I21" s="2">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>25</v>
+      </c>
+      <c r="K21" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11">
+      <c r="B22" t="s">
+        <v>20</v>
+      </c>
+      <c r="D22">
+        <v>433</v>
+      </c>
+      <c r="E22">
+        <v>0</v>
+      </c>
+      <c r="F22">
+        <v>433</v>
+      </c>
+      <c r="G22" s="1">
+        <v>0</v>
+      </c>
+      <c r="H22" s="1">
+        <v>100</v>
+      </c>
+      <c r="I22" s="2">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>433</v>
+      </c>
+      <c r="K22" s="1">
+        <v>100</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:K22"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="30.7109375" customWidth="1"/>
+    <col min="2" max="2" width="30.7109375" customWidth="1"/>
+    <col min="7" max="8" width="9.140625" style="1"/>
+    <col min="9" max="9" width="9.140625" style="2"/>
+    <col min="11" max="11" width="9.140625" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11">
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11">
+      <c r="A2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D2">
+        <v>38</v>
+      </c>
+      <c r="E2">
         <v>32</v>
       </c>
       <c r="F2">

--- a/academias/Biología - Estadisticos 20222.xlsx
+++ b/academias/Biología - Estadisticos 20222.xlsx
@@ -849,19 +849,19 @@
         <v>28</v>
       </c>
       <c r="E11">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F11">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G11" s="1">
-        <v>71.40000000000001</v>
+        <v>75</v>
       </c>
       <c r="H11" s="1">
-        <v>28.6</v>
+        <v>25</v>
       </c>
       <c r="I11" s="2">
-        <v>8.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J11">
         <v>0</v>
@@ -951,16 +951,16 @@
         <v>125</v>
       </c>
       <c r="E14">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F14">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G14" s="1">
-        <v>88</v>
+        <v>88.8</v>
       </c>
       <c r="H14" s="1">
-        <v>12</v>
+        <v>11.2</v>
       </c>
       <c r="I14" s="2">
         <v>8.699999999999999</v>
@@ -1219,16 +1219,16 @@
         <v>433</v>
       </c>
       <c r="E22">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="F22">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G22" s="1">
-        <v>83.59999999999999</v>
+        <v>83.8</v>
       </c>
       <c r="H22" s="1">
-        <v>16.4</v>
+        <v>16.2</v>
       </c>
       <c r="I22" s="2">
         <v>8</v>
@@ -1306,25 +1306,25 @@
         <v>38</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="F2">
-        <v>38</v>
+        <v>7</v>
       </c>
       <c r="G2" s="1">
-        <v>0</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="H2" s="1">
-        <v>100</v>
+        <v>18.4</v>
       </c>
       <c r="I2" s="2">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="J2">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="K2" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -1341,25 +1341,25 @@
         <v>32</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="F3">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="G3" s="1">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="H3" s="1">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="I3" s="2">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="J3">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="K3" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -1373,25 +1373,25 @@
         <v>70</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="F4">
-        <v>70</v>
+        <v>15</v>
       </c>
       <c r="G4" s="1">
-        <v>0</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="H4" s="1">
-        <v>100</v>
+        <v>21.4</v>
       </c>
       <c r="I4" s="2">
-        <v>0</v>
+        <v>7.9</v>
       </c>
       <c r="J4">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="K4" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -1577,25 +1577,25 @@
         <v>31</v>
       </c>
       <c r="E10">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="F10">
-        <v>31</v>
+        <v>8</v>
       </c>
       <c r="G10" s="1">
-        <v>0</v>
+        <v>74.2</v>
       </c>
       <c r="H10" s="1">
-        <v>100</v>
+        <v>25.8</v>
       </c>
       <c r="I10" s="2">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="J10">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="K10" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -1612,25 +1612,25 @@
         <v>28</v>
       </c>
       <c r="E11">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="F11">
-        <v>28</v>
+        <v>4</v>
       </c>
       <c r="G11" s="1">
-        <v>0</v>
+        <v>85.7</v>
       </c>
       <c r="H11" s="1">
-        <v>100</v>
+        <v>14.3</v>
       </c>
       <c r="I11" s="2">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="J11">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="K11" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -1647,25 +1647,25 @@
         <v>34</v>
       </c>
       <c r="E12">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="F12">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="G12" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H12" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I12" s="2">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="J12">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="K12" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:11">
@@ -1682,25 +1682,25 @@
         <v>32</v>
       </c>
       <c r="E13">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="F13">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="G13" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H13" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I13" s="2">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="J13">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="K13" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -1714,25 +1714,25 @@
         <v>125</v>
       </c>
       <c r="E14">
-        <v>0</v>
+        <v>113</v>
       </c>
       <c r="F14">
-        <v>125</v>
+        <v>12</v>
       </c>
       <c r="G14" s="1">
-        <v>0</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="H14" s="1">
-        <v>100</v>
+        <v>9.6</v>
       </c>
       <c r="I14" s="2">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J14">
-        <v>125</v>
+        <v>0</v>
       </c>
       <c r="K14" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -1982,25 +1982,25 @@
         <v>433</v>
       </c>
       <c r="E22">
-        <v>0</v>
+        <v>168</v>
       </c>
       <c r="F22">
-        <v>433</v>
+        <v>265</v>
       </c>
       <c r="G22" s="1">
-        <v>0</v>
+        <v>38.8</v>
       </c>
       <c r="H22" s="1">
-        <v>100</v>
+        <v>61.2</v>
       </c>
       <c r="I22" s="2">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="J22">
-        <v>433</v>
+        <v>238</v>
       </c>
       <c r="K22" s="1">
-        <v>100</v>
+        <v>55</v>
       </c>
     </row>
   </sheetData>
@@ -2069,19 +2069,19 @@
         <v>38</v>
       </c>
       <c r="E2">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G2" s="1">
-        <v>84.2</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="H2" s="1">
-        <v>15.8</v>
+        <v>18.4</v>
       </c>
       <c r="I2" s="2">
-        <v>7.7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J2">
         <v>0</v>
@@ -2104,19 +2104,19 @@
         <v>32</v>
       </c>
       <c r="E3">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F3">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G3" s="1">
-        <v>71.90000000000001</v>
+        <v>75</v>
       </c>
       <c r="H3" s="1">
-        <v>28.1</v>
+        <v>25</v>
       </c>
       <c r="I3" s="2">
-        <v>6.5</v>
+        <v>7.1</v>
       </c>
       <c r="J3">
         <v>0</v>
@@ -2148,7 +2148,7 @@
         <v>21.4</v>
       </c>
       <c r="I4" s="2">
-        <v>7.1</v>
+        <v>7.6</v>
       </c>
       <c r="J4">
         <v>0</v>
@@ -2340,19 +2340,19 @@
         <v>31</v>
       </c>
       <c r="E10">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="F10">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G10" s="1">
-        <v>80.59999999999999</v>
+        <v>74.2</v>
       </c>
       <c r="H10" s="1">
-        <v>19.4</v>
+        <v>25.8</v>
       </c>
       <c r="I10" s="2">
-        <v>7.9</v>
+        <v>7.6</v>
       </c>
       <c r="J10">
         <v>0</v>
@@ -2375,16 +2375,16 @@
         <v>28</v>
       </c>
       <c r="E11">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="F11">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="G11" s="1">
-        <v>71.40000000000001</v>
+        <v>85.7</v>
       </c>
       <c r="H11" s="1">
-        <v>28.6</v>
+        <v>14.3</v>
       </c>
       <c r="I11" s="2">
         <v>8.1</v>
@@ -2410,16 +2410,16 @@
         <v>34</v>
       </c>
       <c r="E12">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G12" s="1">
-        <v>97.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="H12" s="1">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="I12" s="2">
         <v>9</v>
@@ -2457,7 +2457,7 @@
         <v>0</v>
       </c>
       <c r="I13" s="2">
-        <v>9.800000000000001</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J13">
         <v>0</v>
@@ -2477,19 +2477,19 @@
         <v>125</v>
       </c>
       <c r="E14">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="F14">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="G14" s="1">
-        <v>88</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="H14" s="1">
-        <v>12</v>
+        <v>9.6</v>
       </c>
       <c r="I14" s="2">
-        <v>8.699999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="J14">
         <v>0</v>
@@ -2745,16 +2745,16 @@
         <v>433</v>
       </c>
       <c r="E22">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="F22">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="G22" s="1">
-        <v>83.59999999999999</v>
+        <v>84.3</v>
       </c>
       <c r="H22" s="1">
-        <v>16.4</v>
+        <v>15.7</v>
       </c>
       <c r="I22" s="2">
         <v>8</v>

--- a/academias/Biología - Estadisticos 20222.xlsx
+++ b/academias/Biología - Estadisticos 20222.xlsx
@@ -645,25 +645,25 @@
         <v>34</v>
       </c>
       <c r="E5">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F5">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G5" s="1">
-        <v>76.5</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="H5" s="1">
-        <v>23.5</v>
+        <v>20.6</v>
       </c>
       <c r="I5" s="2">
         <v>7.1</v>
       </c>
       <c r="J5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K5" s="1">
-        <v>2.94</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -680,25 +680,25 @@
         <v>30</v>
       </c>
       <c r="E6">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F6">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G6" s="1">
-        <v>80</v>
+        <v>83.3</v>
       </c>
       <c r="H6" s="1">
-        <v>20</v>
+        <v>16.7</v>
       </c>
       <c r="I6" s="2">
         <v>7.1</v>
       </c>
       <c r="J6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K6" s="1">
-        <v>3.33</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -712,25 +712,25 @@
         <v>64</v>
       </c>
       <c r="E7">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F7">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G7" s="1">
-        <v>78.09999999999999</v>
+        <v>81.2</v>
       </c>
       <c r="H7" s="1">
-        <v>21.9</v>
+        <v>18.8</v>
       </c>
       <c r="I7" s="2">
         <v>7.1</v>
       </c>
       <c r="J7">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K7" s="1">
-        <v>3.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -1219,25 +1219,25 @@
         <v>433</v>
       </c>
       <c r="E22">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="F22">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="G22" s="1">
-        <v>83.8</v>
+        <v>84.3</v>
       </c>
       <c r="H22" s="1">
-        <v>16.2</v>
+        <v>15.7</v>
       </c>
       <c r="I22" s="2">
         <v>8</v>
       </c>
       <c r="J22">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K22" s="1">
-        <v>0.5</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1408,25 +1408,25 @@
         <v>34</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="F5">
-        <v>34</v>
+        <v>7</v>
       </c>
       <c r="G5" s="1">
-        <v>0</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="H5" s="1">
-        <v>100</v>
+        <v>20.6</v>
       </c>
       <c r="I5" s="2">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="J5">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="K5" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -1443,25 +1443,25 @@
         <v>30</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="F6">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="G6" s="1">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="H6" s="1">
-        <v>100</v>
+        <v>20</v>
       </c>
       <c r="I6" s="2">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="J6">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K6" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -1475,25 +1475,25 @@
         <v>64</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="F7">
-        <v>64</v>
+        <v>13</v>
       </c>
       <c r="G7" s="1">
-        <v>0</v>
+        <v>79.7</v>
       </c>
       <c r="H7" s="1">
-        <v>100</v>
+        <v>20.3</v>
       </c>
       <c r="I7" s="2">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J7">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="K7" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -1510,25 +1510,25 @@
         <v>26</v>
       </c>
       <c r="E8">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="F8">
-        <v>26</v>
+        <v>2</v>
       </c>
       <c r="G8" s="1">
-        <v>0</v>
+        <v>92.3</v>
       </c>
       <c r="H8" s="1">
-        <v>100</v>
+        <v>7.7</v>
       </c>
       <c r="I8" s="2">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="J8">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="K8" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -1542,25 +1542,25 @@
         <v>26</v>
       </c>
       <c r="E9">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="F9">
-        <v>26</v>
+        <v>2</v>
       </c>
       <c r="G9" s="1">
-        <v>0</v>
+        <v>92.3</v>
       </c>
       <c r="H9" s="1">
-        <v>100</v>
+        <v>7.7</v>
       </c>
       <c r="I9" s="2">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="J9">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="K9" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -1749,25 +1749,25 @@
         <v>41</v>
       </c>
       <c r="E15">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="F15">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="G15" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H15" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I15" s="2">
-        <v>0</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J15">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="K15" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -1784,25 +1784,25 @@
         <v>27</v>
       </c>
       <c r="E16">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="F16">
-        <v>27</v>
+        <v>1</v>
       </c>
       <c r="G16" s="1">
-        <v>0</v>
+        <v>96.3</v>
       </c>
       <c r="H16" s="1">
-        <v>100</v>
+        <v>3.7</v>
       </c>
       <c r="I16" s="2">
-        <v>0</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J16">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="K16" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:11">
@@ -1819,25 +1819,25 @@
         <v>41</v>
       </c>
       <c r="E17">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="F17">
-        <v>41</v>
+        <v>4</v>
       </c>
       <c r="G17" s="1">
-        <v>0</v>
+        <v>90.2</v>
       </c>
       <c r="H17" s="1">
-        <v>100</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="I17" s="2">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="J17">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="K17" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:11">
@@ -1854,25 +1854,25 @@
         <v>14</v>
       </c>
       <c r="E18">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F18">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="G18" s="1">
-        <v>0</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="H18" s="1">
-        <v>100</v>
+        <v>28.6</v>
       </c>
       <c r="I18" s="2">
-        <v>0</v>
+        <v>6.9</v>
       </c>
       <c r="J18">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="K18" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:11">
@@ -1886,25 +1886,25 @@
         <v>123</v>
       </c>
       <c r="E19">
-        <v>0</v>
+        <v>114</v>
       </c>
       <c r="F19">
-        <v>123</v>
+        <v>9</v>
       </c>
       <c r="G19" s="1">
-        <v>0</v>
+        <v>92.7</v>
       </c>
       <c r="H19" s="1">
-        <v>100</v>
+        <v>7.3</v>
       </c>
       <c r="I19" s="2">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="J19">
-        <v>123</v>
+        <v>0</v>
       </c>
       <c r="K19" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:11">
@@ -1982,25 +1982,25 @@
         <v>433</v>
       </c>
       <c r="E22">
-        <v>168</v>
+        <v>357</v>
       </c>
       <c r="F22">
-        <v>265</v>
+        <v>76</v>
       </c>
       <c r="G22" s="1">
-        <v>38.8</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="H22" s="1">
-        <v>61.2</v>
+        <v>17.6</v>
       </c>
       <c r="I22" s="2">
-        <v>3.5</v>
+        <v>7.4</v>
       </c>
       <c r="J22">
-        <v>238</v>
+        <v>25</v>
       </c>
       <c r="K22" s="1">
-        <v>55</v>
+        <v>5.8</v>
       </c>
     </row>
   </sheetData>
@@ -2171,25 +2171,25 @@
         <v>34</v>
       </c>
       <c r="E5">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F5">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G5" s="1">
-        <v>76.5</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="H5" s="1">
-        <v>23.5</v>
+        <v>20.6</v>
       </c>
       <c r="I5" s="2">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K5" s="1">
-        <v>2.94</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -2218,13 +2218,13 @@
         <v>20</v>
       </c>
       <c r="I6" s="2">
-        <v>7.1</v>
+        <v>7.4</v>
       </c>
       <c r="J6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K6" s="1">
-        <v>3.33</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -2238,25 +2238,25 @@
         <v>64</v>
       </c>
       <c r="E7">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F7">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G7" s="1">
-        <v>78.09999999999999</v>
+        <v>79.7</v>
       </c>
       <c r="H7" s="1">
-        <v>21.9</v>
+        <v>20.3</v>
       </c>
       <c r="I7" s="2">
-        <v>7.1</v>
+        <v>7.2</v>
       </c>
       <c r="J7">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K7" s="1">
-        <v>3.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -2273,19 +2273,19 @@
         <v>26</v>
       </c>
       <c r="E8">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G8" s="1">
-        <v>96.2</v>
+        <v>92.3</v>
       </c>
       <c r="H8" s="1">
-        <v>3.8</v>
+        <v>7.7</v>
       </c>
       <c r="I8" s="2">
-        <v>9.1</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J8">
         <v>0</v>
@@ -2305,19 +2305,19 @@
         <v>26</v>
       </c>
       <c r="E9">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G9" s="1">
-        <v>96.2</v>
+        <v>92.3</v>
       </c>
       <c r="H9" s="1">
-        <v>3.8</v>
+        <v>7.7</v>
       </c>
       <c r="I9" s="2">
-        <v>9.1</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J9">
         <v>0</v>
@@ -2524,7 +2524,7 @@
         <v>0</v>
       </c>
       <c r="I15" s="2">
-        <v>9.300000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="J15">
         <v>0</v>
@@ -2547,19 +2547,19 @@
         <v>27</v>
       </c>
       <c r="E16">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F16">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G16" s="1">
-        <v>92.59999999999999</v>
+        <v>96.3</v>
       </c>
       <c r="H16" s="1">
-        <v>7.4</v>
+        <v>3.7</v>
       </c>
       <c r="I16" s="2">
-        <v>8.699999999999999</v>
+        <v>9.1</v>
       </c>
       <c r="J16">
         <v>0</v>
@@ -2582,19 +2582,19 @@
         <v>41</v>
       </c>
       <c r="E17">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F17">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G17" s="1">
-        <v>95.09999999999999</v>
+        <v>90.2</v>
       </c>
       <c r="H17" s="1">
-        <v>4.9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="I17" s="2">
-        <v>8.699999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J17">
         <v>0</v>
@@ -2617,19 +2617,19 @@
         <v>14</v>
       </c>
       <c r="E18">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F18">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G18" s="1">
-        <v>57.1</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="H18" s="1">
-        <v>42.9</v>
+        <v>28.6</v>
       </c>
       <c r="I18" s="2">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="J18">
         <v>0</v>
@@ -2649,19 +2649,19 @@
         <v>123</v>
       </c>
       <c r="E19">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F19">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G19" s="1">
-        <v>91.90000000000001</v>
+        <v>92.7</v>
       </c>
       <c r="H19" s="1">
-        <v>8.1</v>
+        <v>7.3</v>
       </c>
       <c r="I19" s="2">
-        <v>8.300000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="J19">
         <v>0</v>
@@ -2745,25 +2745,25 @@
         <v>433</v>
       </c>
       <c r="E22">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="F22">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G22" s="1">
-        <v>84.3</v>
+        <v>84.5</v>
       </c>
       <c r="H22" s="1">
-        <v>15.7</v>
+        <v>15.5</v>
       </c>
       <c r="I22" s="2">
-        <v>8</v>
+        <v>8.1</v>
       </c>
       <c r="J22">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K22" s="1">
-        <v>0.5</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/academias/Biología - Estadisticos 20222.xlsx
+++ b/academias/Biología - Estadisticos 20222.xlsx
@@ -1921,25 +1921,25 @@
         <v>25</v>
       </c>
       <c r="E20">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F20">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="G20" s="1">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="H20" s="1">
-        <v>100</v>
+        <v>68</v>
       </c>
       <c r="I20" s="2">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="J20">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="K20" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:11">
@@ -1953,25 +1953,25 @@
         <v>25</v>
       </c>
       <c r="E21">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F21">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="G21" s="1">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="H21" s="1">
-        <v>100</v>
+        <v>68</v>
       </c>
       <c r="I21" s="2">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="J21">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="K21" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:11">
@@ -1982,25 +1982,25 @@
         <v>433</v>
       </c>
       <c r="E22">
-        <v>357</v>
+        <v>365</v>
       </c>
       <c r="F22">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="G22" s="1">
-        <v>82.40000000000001</v>
+        <v>84.3</v>
       </c>
       <c r="H22" s="1">
-        <v>17.6</v>
+        <v>15.7</v>
       </c>
       <c r="I22" s="2">
-        <v>7.4</v>
+        <v>7.9</v>
       </c>
       <c r="J22">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="K22" s="1">
-        <v>5.8</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -2684,16 +2684,16 @@
         <v>25</v>
       </c>
       <c r="E20">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F20">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G20" s="1">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="H20" s="1">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="I20" s="2">
         <v>6.1</v>
@@ -2716,16 +2716,16 @@
         <v>25</v>
       </c>
       <c r="E21">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F21">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G21" s="1">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="H21" s="1">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="I21" s="2">
         <v>6.1</v>
@@ -2745,16 +2745,16 @@
         <v>433</v>
       </c>
       <c r="E22">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="F22">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G22" s="1">
-        <v>84.5</v>
+        <v>84.3</v>
       </c>
       <c r="H22" s="1">
-        <v>15.5</v>
+        <v>15.7</v>
       </c>
       <c r="I22" s="2">
         <v>8.1</v>

--- a/academias/Biología - Estadisticos 20222.xlsx
+++ b/academias/Biología - Estadisticos 20222.xlsx
@@ -1250,8 +1250,7 @@
   <dimension ref="A1:K22"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="30.7109375" customWidth="1"/>
-    <col min="2" max="2" width="30.7109375" customWidth="1"/>
+    <col min="1" max="2" width="30.7109375" customWidth="1"/>
     <col min="7" max="8" width="9.140625" style="1"/>
     <col min="9" max="9" width="9.140625" style="2"/>
     <col min="11" max="11" width="9.140625" style="1"/>
@@ -1694,7 +1693,7 @@
         <v>0</v>
       </c>
       <c r="I13" s="2">
-        <v>9.4</v>
+        <v>9.5</v>
       </c>
       <c r="J13">
         <v>0</v>
@@ -2013,8 +2012,7 @@
   <dimension ref="A1:K22"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="30.7109375" customWidth="1"/>
-    <col min="2" max="2" width="30.7109375" customWidth="1"/>
+    <col min="1" max="2" width="30.7109375" customWidth="1"/>
     <col min="7" max="8" width="9.140625" style="1"/>
     <col min="9" max="9" width="9.140625" style="2"/>
     <col min="11" max="11" width="9.140625" style="1"/>
@@ -2183,7 +2181,7 @@
         <v>20.6</v>
       </c>
       <c r="I5" s="2">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="J5">
         <v>0</v>
@@ -2206,19 +2204,19 @@
         <v>30</v>
       </c>
       <c r="E6">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F6">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G6" s="1">
-        <v>80</v>
+        <v>83.3</v>
       </c>
       <c r="H6" s="1">
-        <v>20</v>
+        <v>16.7</v>
       </c>
       <c r="I6" s="2">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="J6">
         <v>0</v>
@@ -2238,19 +2236,19 @@
         <v>64</v>
       </c>
       <c r="E7">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F7">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G7" s="1">
-        <v>79.7</v>
+        <v>81.2</v>
       </c>
       <c r="H7" s="1">
-        <v>20.3</v>
+        <v>18.8</v>
       </c>
       <c r="I7" s="2">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="J7">
         <v>0</v>
@@ -2273,19 +2271,19 @@
         <v>26</v>
       </c>
       <c r="E8">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G8" s="1">
-        <v>92.3</v>
+        <v>96.2</v>
       </c>
       <c r="H8" s="1">
-        <v>7.7</v>
+        <v>3.8</v>
       </c>
       <c r="I8" s="2">
-        <v>8.300000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="J8">
         <v>0</v>
@@ -2305,19 +2303,19 @@
         <v>26</v>
       </c>
       <c r="E9">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G9" s="1">
-        <v>92.3</v>
+        <v>96.2</v>
       </c>
       <c r="H9" s="1">
-        <v>7.7</v>
+        <v>3.8</v>
       </c>
       <c r="I9" s="2">
-        <v>8.300000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="J9">
         <v>0</v>
@@ -2340,19 +2338,19 @@
         <v>31</v>
       </c>
       <c r="E10">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F10">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G10" s="1">
-        <v>74.2</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="H10" s="1">
-        <v>25.8</v>
+        <v>22.6</v>
       </c>
       <c r="I10" s="2">
-        <v>7.6</v>
+        <v>7.3</v>
       </c>
       <c r="J10">
         <v>0</v>
@@ -2387,7 +2385,7 @@
         <v>14.3</v>
       </c>
       <c r="I11" s="2">
-        <v>8.1</v>
+        <v>8</v>
       </c>
       <c r="J11">
         <v>0</v>
@@ -2457,7 +2455,7 @@
         <v>0</v>
       </c>
       <c r="I13" s="2">
-        <v>9.699999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J13">
         <v>0</v>
@@ -2477,19 +2475,19 @@
         <v>125</v>
       </c>
       <c r="E14">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F14">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G14" s="1">
-        <v>90.40000000000001</v>
+        <v>91.2</v>
       </c>
       <c r="H14" s="1">
-        <v>9.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I14" s="2">
-        <v>8.6</v>
+        <v>8.5</v>
       </c>
       <c r="J14">
         <v>0</v>
@@ -2524,7 +2522,7 @@
         <v>0</v>
       </c>
       <c r="I15" s="2">
-        <v>9.6</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J15">
         <v>0</v>
@@ -2547,19 +2545,19 @@
         <v>27</v>
       </c>
       <c r="E16">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F16">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G16" s="1">
-        <v>96.3</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="H16" s="1">
-        <v>3.7</v>
+        <v>7.4</v>
       </c>
       <c r="I16" s="2">
-        <v>9.1</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J16">
         <v>0</v>
@@ -2582,19 +2580,19 @@
         <v>41</v>
       </c>
       <c r="E17">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="F17">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G17" s="1">
-        <v>90.2</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="H17" s="1">
-        <v>9.800000000000001</v>
+        <v>14.6</v>
       </c>
       <c r="I17" s="2">
-        <v>8.800000000000001</v>
+        <v>8.1</v>
       </c>
       <c r="J17">
         <v>0</v>
@@ -2629,7 +2627,7 @@
         <v>28.6</v>
       </c>
       <c r="I18" s="2">
-        <v>6.8</v>
+        <v>6.5</v>
       </c>
       <c r="J18">
         <v>0</v>
@@ -2649,19 +2647,19 @@
         <v>123</v>
       </c>
       <c r="E19">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="F19">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="G19" s="1">
-        <v>92.7</v>
+        <v>90.2</v>
       </c>
       <c r="H19" s="1">
-        <v>7.3</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="I19" s="2">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J19">
         <v>0</v>
@@ -2757,7 +2755,7 @@
         <v>15.7</v>
       </c>
       <c r="I22" s="2">
-        <v>8.1</v>
+        <v>7.9</v>
       </c>
       <c r="J22">
         <v>0</v>

--- a/academias/Biología - Estadisticos 20222.xlsx
+++ b/academias/Biología - Estadisticos 20222.xlsx
@@ -2102,16 +2102,16 @@
         <v>32</v>
       </c>
       <c r="E3">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="F3">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="G3" s="1">
-        <v>75</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="H3" s="1">
-        <v>25</v>
+        <v>9.4</v>
       </c>
       <c r="I3" s="2">
         <v>7.1</v>
@@ -2134,16 +2134,16 @@
         <v>70</v>
       </c>
       <c r="E4">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="F4">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="G4" s="1">
-        <v>78.59999999999999</v>
+        <v>85.7</v>
       </c>
       <c r="H4" s="1">
-        <v>21.4</v>
+        <v>14.3</v>
       </c>
       <c r="I4" s="2">
         <v>7.6</v>
@@ -2743,16 +2743,16 @@
         <v>433</v>
       </c>
       <c r="E22">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="F22">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="G22" s="1">
-        <v>84.3</v>
+        <v>85.5</v>
       </c>
       <c r="H22" s="1">
-        <v>15.7</v>
+        <v>14.5</v>
       </c>
       <c r="I22" s="2">
         <v>7.9</v>

--- a/academias/Biología - Estadisticos 20222.xlsx
+++ b/academias/Biología - Estadisticos 20222.xlsx
@@ -2682,19 +2682,19 @@
         <v>25</v>
       </c>
       <c r="E20">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="F20">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="G20" s="1">
-        <v>32</v>
+        <v>64</v>
       </c>
       <c r="H20" s="1">
-        <v>68</v>
+        <v>36</v>
       </c>
       <c r="I20" s="2">
-        <v>6.1</v>
+        <v>6.4</v>
       </c>
       <c r="J20">
         <v>0</v>
@@ -2714,19 +2714,19 @@
         <v>25</v>
       </c>
       <c r="E21">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="F21">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="G21" s="1">
-        <v>32</v>
+        <v>64</v>
       </c>
       <c r="H21" s="1">
-        <v>68</v>
+        <v>36</v>
       </c>
       <c r="I21" s="2">
-        <v>6.1</v>
+        <v>6.4</v>
       </c>
       <c r="J21">
         <v>0</v>
@@ -2743,16 +2743,16 @@
         <v>433</v>
       </c>
       <c r="E22">
-        <v>370</v>
+        <v>378</v>
       </c>
       <c r="F22">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="G22" s="1">
-        <v>85.5</v>
+        <v>87.3</v>
       </c>
       <c r="H22" s="1">
-        <v>14.5</v>
+        <v>12.7</v>
       </c>
       <c r="I22" s="2">
         <v>7.9</v>
